--- a/Data/Fishing_sessions.xlsx
+++ b/Data/Fishing_sessions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10808"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10911"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/victorbrun/Documents/travail/These/Travaux/Food SFB/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anna/Desktop/Shama/Fishing Logbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37693803-8C88-0549-932A-3FAB86BE2E0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B46126E8-1812-814B-807C-E3F0EED45577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="25500" windowHeight="14380" activeTab="1" xr2:uid="{34E003D3-D964-0343-936F-E3BB10C1D646}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="21420" windowHeight="16320" activeTab="1" xr2:uid="{34E003D3-D964-0343-936F-E3BB10C1D646}"/>
   </bookViews>
   <sheets>
     <sheet name="Landings" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13674" uniqueCount="1568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14900" uniqueCount="1817">
   <si>
     <t>Date</t>
   </si>
@@ -4731,13 +4731,760 @@
   </si>
   <si>
     <t>ID</t>
+  </si>
+  <si>
+    <t>In front of Depla</t>
+  </si>
+  <si>
+    <t>Mababaw</t>
+  </si>
+  <si>
+    <t>DODONG</t>
+  </si>
+  <si>
+    <t>Cayangag Island</t>
+  </si>
+  <si>
+    <t>Rakit-rakit</t>
+  </si>
+  <si>
+    <t>D815</t>
+  </si>
+  <si>
+    <t>D816</t>
+  </si>
+  <si>
+    <t>FRANKLEN</t>
+  </si>
+  <si>
+    <t>D817</t>
+  </si>
+  <si>
+    <t>D818</t>
+  </si>
+  <si>
+    <t>D819</t>
+  </si>
+  <si>
+    <t>RUNLIASI</t>
+  </si>
+  <si>
+    <t>D820</t>
+  </si>
+  <si>
+    <t>JORCURSI</t>
+  </si>
+  <si>
+    <t>D821</t>
+  </si>
+  <si>
+    <t>TOTLUMSI</t>
+  </si>
+  <si>
+    <t>D822</t>
+  </si>
+  <si>
+    <t>EDITULSI</t>
+  </si>
+  <si>
+    <t>D823</t>
+  </si>
+  <si>
+    <t>NILABESI</t>
+  </si>
+  <si>
+    <t>D824</t>
+  </si>
+  <si>
+    <t>MATBARSI</t>
+  </si>
+  <si>
+    <t>D825</t>
+  </si>
+  <si>
+    <t>BONBERSI</t>
+  </si>
+  <si>
+    <t>D826</t>
+  </si>
+  <si>
+    <t>BOKOABSI</t>
+  </si>
+  <si>
+    <t>D827</t>
+  </si>
+  <si>
+    <t>GERDELSI</t>
+  </si>
+  <si>
+    <t>D828</t>
+  </si>
+  <si>
+    <t>D829</t>
+  </si>
+  <si>
+    <t>JONJAGSA</t>
+  </si>
+  <si>
+    <t>D830</t>
+  </si>
+  <si>
+    <t>WELRADSA</t>
+  </si>
+  <si>
+    <t>D831</t>
+  </si>
+  <si>
+    <t>JOJPATSA</t>
+  </si>
+  <si>
+    <t>D832</t>
+  </si>
+  <si>
+    <t>D833</t>
+  </si>
+  <si>
+    <t>HISYILSA</t>
+  </si>
+  <si>
+    <t>D834</t>
+  </si>
+  <si>
+    <t>D835</t>
+  </si>
+  <si>
+    <t>D836</t>
+  </si>
+  <si>
+    <t>ADEDALSA</t>
+  </si>
+  <si>
+    <t>D837</t>
+  </si>
+  <si>
+    <t>NAPRECSA</t>
+  </si>
+  <si>
+    <t>D838</t>
+  </si>
+  <si>
+    <t>JERBALSA</t>
+  </si>
+  <si>
+    <t>D839</t>
+  </si>
+  <si>
+    <t>D840</t>
+  </si>
+  <si>
+    <t>D841</t>
+  </si>
+  <si>
+    <t>D842</t>
+  </si>
+  <si>
+    <t>D843</t>
+  </si>
+  <si>
+    <t>D844</t>
+  </si>
+  <si>
+    <t>D845</t>
+  </si>
+  <si>
+    <t>D846</t>
+  </si>
+  <si>
+    <t>D847</t>
+  </si>
+  <si>
+    <t>D848</t>
+  </si>
+  <si>
+    <t>D849</t>
+  </si>
+  <si>
+    <t>D850</t>
+  </si>
+  <si>
+    <t>D851</t>
+  </si>
+  <si>
+    <t>D852</t>
+  </si>
+  <si>
+    <t>D853</t>
+  </si>
+  <si>
+    <t>D854</t>
+  </si>
+  <si>
+    <t>D855</t>
+  </si>
+  <si>
+    <t>D856</t>
+  </si>
+  <si>
+    <t>D857</t>
+  </si>
+  <si>
+    <t>D858</t>
+  </si>
+  <si>
+    <t>D859</t>
+  </si>
+  <si>
+    <t>D860</t>
+  </si>
+  <si>
+    <t>D861</t>
+  </si>
+  <si>
+    <t>D862</t>
+  </si>
+  <si>
+    <t>D863</t>
+  </si>
+  <si>
+    <t>D864</t>
+  </si>
+  <si>
+    <t>D865</t>
+  </si>
+  <si>
+    <t>D866</t>
+  </si>
+  <si>
+    <t>D867</t>
+  </si>
+  <si>
+    <t>D868</t>
+  </si>
+  <si>
+    <t>D869</t>
+  </si>
+  <si>
+    <t>D870</t>
+  </si>
+  <si>
+    <t>D871</t>
+  </si>
+  <si>
+    <t>D872</t>
+  </si>
+  <si>
+    <t>D873</t>
+  </si>
+  <si>
+    <t>D874</t>
+  </si>
+  <si>
+    <t>D875</t>
+  </si>
+  <si>
+    <t>D876</t>
+  </si>
+  <si>
+    <t>D877</t>
+  </si>
+  <si>
+    <t>D878</t>
+  </si>
+  <si>
+    <t>D879</t>
+  </si>
+  <si>
+    <t>D880</t>
+  </si>
+  <si>
+    <t>D881</t>
+  </si>
+  <si>
+    <t>D882</t>
+  </si>
+  <si>
+    <t>D883</t>
+  </si>
+  <si>
+    <t>D884</t>
+  </si>
+  <si>
+    <t>D885</t>
+  </si>
+  <si>
+    <t>D886</t>
+  </si>
+  <si>
+    <t>D887</t>
+  </si>
+  <si>
+    <t>D888</t>
+  </si>
+  <si>
+    <t>D889</t>
+  </si>
+  <si>
+    <t>D890</t>
+  </si>
+  <si>
+    <t>D891</t>
+  </si>
+  <si>
+    <t>D892</t>
+  </si>
+  <si>
+    <t>D893</t>
+  </si>
+  <si>
+    <t>D894</t>
+  </si>
+  <si>
+    <t>D895</t>
+  </si>
+  <si>
+    <t>D896</t>
+  </si>
+  <si>
+    <t>D897</t>
+  </si>
+  <si>
+    <t>D898</t>
+  </si>
+  <si>
+    <t>D899</t>
+  </si>
+  <si>
+    <t>D900</t>
+  </si>
+  <si>
+    <t>D901</t>
+  </si>
+  <si>
+    <t>D902</t>
+  </si>
+  <si>
+    <t>D903</t>
+  </si>
+  <si>
+    <t>RIOCALSA</t>
+  </si>
+  <si>
+    <t>NORABRSA</t>
+  </si>
+  <si>
+    <t>ROTDALSA</t>
+  </si>
+  <si>
+    <t>REGRADDE</t>
+  </si>
+  <si>
+    <t>DODONGDE</t>
+  </si>
+  <si>
+    <t>EDERADDE</t>
+  </si>
+  <si>
+    <t>Mayniog</t>
+  </si>
+  <si>
+    <t>PANMABDE</t>
+  </si>
+  <si>
+    <t>Kayangag</t>
+  </si>
+  <si>
+    <t>EDETABDE</t>
+  </si>
+  <si>
+    <t>JIMJASDE</t>
+  </si>
+  <si>
+    <t>RODPADDE</t>
+  </si>
+  <si>
+    <t>JAIBUTDE</t>
+  </si>
+  <si>
+    <t>In front of Silanga sanctuary</t>
+  </si>
+  <si>
+    <t>NERCABDE</t>
+  </si>
+  <si>
+    <t>RUEHERDE</t>
+  </si>
+  <si>
+    <t>DANJABDE</t>
+  </si>
+  <si>
+    <t>Ubongan</t>
+  </si>
+  <si>
+    <t>D904</t>
+  </si>
+  <si>
+    <t>D905</t>
+  </si>
+  <si>
+    <t>D906</t>
+  </si>
+  <si>
+    <t>D907</t>
+  </si>
+  <si>
+    <t>D908</t>
+  </si>
+  <si>
+    <t>D909</t>
+  </si>
+  <si>
+    <t>D910</t>
+  </si>
+  <si>
+    <t>D911</t>
+  </si>
+  <si>
+    <t>D912</t>
+  </si>
+  <si>
+    <t>D913</t>
+  </si>
+  <si>
+    <t>D914</t>
+  </si>
+  <si>
+    <t>D915</t>
+  </si>
+  <si>
+    <t>D916</t>
+  </si>
+  <si>
+    <t>D917</t>
+  </si>
+  <si>
+    <t>D918</t>
+  </si>
+  <si>
+    <t>D919</t>
+  </si>
+  <si>
+    <t>D920</t>
+  </si>
+  <si>
+    <t>D921</t>
+  </si>
+  <si>
+    <t>D922</t>
+  </si>
+  <si>
+    <t>D923</t>
+  </si>
+  <si>
+    <t>D924</t>
+  </si>
+  <si>
+    <t>D925</t>
+  </si>
+  <si>
+    <t>D926</t>
+  </si>
+  <si>
+    <t>D927</t>
+  </si>
+  <si>
+    <t>D928</t>
+  </si>
+  <si>
+    <t>D929</t>
+  </si>
+  <si>
+    <t>D930</t>
+  </si>
+  <si>
+    <t>D931</t>
+  </si>
+  <si>
+    <t>D932</t>
+  </si>
+  <si>
+    <t>D933</t>
+  </si>
+  <si>
+    <t>D934</t>
+  </si>
+  <si>
+    <t>D935</t>
+  </si>
+  <si>
+    <t>D936</t>
+  </si>
+  <si>
+    <t>D937</t>
+  </si>
+  <si>
+    <t>D938</t>
+  </si>
+  <si>
+    <t>D939</t>
+  </si>
+  <si>
+    <t>D940</t>
+  </si>
+  <si>
+    <t>D941</t>
+  </si>
+  <si>
+    <t>D942</t>
+  </si>
+  <si>
+    <t>D943</t>
+  </si>
+  <si>
+    <t>D944</t>
+  </si>
+  <si>
+    <t>D945</t>
+  </si>
+  <si>
+    <t>D946</t>
+  </si>
+  <si>
+    <t>D947</t>
+  </si>
+  <si>
+    <t>D948</t>
+  </si>
+  <si>
+    <t>D949</t>
+  </si>
+  <si>
+    <t>D950</t>
+  </si>
+  <si>
+    <t>D951</t>
+  </si>
+  <si>
+    <t>D952</t>
+  </si>
+  <si>
+    <t>D953</t>
+  </si>
+  <si>
+    <t>D954</t>
+  </si>
+  <si>
+    <t>D955</t>
+  </si>
+  <si>
+    <t>D956</t>
+  </si>
+  <si>
+    <t>D957</t>
+  </si>
+  <si>
+    <t>D958</t>
+  </si>
+  <si>
+    <t>D959</t>
+  </si>
+  <si>
+    <t>D960</t>
+  </si>
+  <si>
+    <t>D961</t>
+  </si>
+  <si>
+    <t>D962</t>
+  </si>
+  <si>
+    <t>D963</t>
+  </si>
+  <si>
+    <t>D964</t>
+  </si>
+  <si>
+    <t>D965</t>
+  </si>
+  <si>
+    <t>D966</t>
+  </si>
+  <si>
+    <t>D967</t>
+  </si>
+  <si>
+    <t>D968</t>
+  </si>
+  <si>
+    <t>D969</t>
+  </si>
+  <si>
+    <t>D970</t>
+  </si>
+  <si>
+    <t>D971</t>
+  </si>
+  <si>
+    <t>D972</t>
+  </si>
+  <si>
+    <t>D973</t>
+  </si>
+  <si>
+    <t>D974</t>
+  </si>
+  <si>
+    <t>D975</t>
+  </si>
+  <si>
+    <t>D976</t>
+  </si>
+  <si>
+    <t>D977</t>
+  </si>
+  <si>
+    <t>D978</t>
+  </si>
+  <si>
+    <t>ROITABDE</t>
+  </si>
+  <si>
+    <t>FRAMABDE</t>
+  </si>
+  <si>
+    <t>RAMCABDE</t>
+  </si>
+  <si>
+    <t>Malenda</t>
+  </si>
+  <si>
+    <t>LOUCARDE</t>
+  </si>
+  <si>
+    <t>ADABADDE</t>
+  </si>
+  <si>
+    <t>In front of MPA</t>
+  </si>
+  <si>
+    <t>At the back of MPA</t>
+  </si>
+  <si>
+    <t>HERTABDE</t>
+  </si>
+  <si>
+    <t>JUNJUNDE</t>
+  </si>
+  <si>
+    <t>RESTABDE</t>
+  </si>
+  <si>
+    <t>GERALDSI</t>
+  </si>
+  <si>
+    <t>NICABESI</t>
+  </si>
+  <si>
+    <t>MATGARSI</t>
+  </si>
+  <si>
+    <t>BOKGABSI</t>
+  </si>
+  <si>
+    <t>RICANDSI</t>
+  </si>
+  <si>
+    <t>MHRANDSI</t>
+  </si>
+  <si>
+    <t>BONCONSI</t>
+  </si>
+  <si>
+    <t>RONMANSI</t>
+  </si>
+  <si>
+    <t>Talacanen</t>
+  </si>
+  <si>
+    <t>EDMGARSI</t>
+  </si>
+  <si>
+    <t>Dingt Bay</t>
+  </si>
+  <si>
+    <t>ARSGARSI</t>
+  </si>
+  <si>
+    <t>Barenben Bay</t>
+  </si>
+  <si>
+    <t>DEOGACSI</t>
+  </si>
+  <si>
+    <t>ERWMORSI</t>
+  </si>
+  <si>
+    <t>JIMLANSI</t>
+  </si>
+  <si>
+    <t>Panalon Bay</t>
+  </si>
+  <si>
+    <t>JILLANSI</t>
+  </si>
+  <si>
+    <t>Cuyocuyo Bay</t>
+  </si>
+  <si>
+    <t>Butuang Bay</t>
+  </si>
+  <si>
+    <t>MARANDSI</t>
+  </si>
+  <si>
+    <t>Imbaludan Bay</t>
+  </si>
+  <si>
+    <t>RICLUMSI</t>
+  </si>
+  <si>
+    <t>RONLIASI</t>
+  </si>
+  <si>
+    <t>LITLANSI</t>
+  </si>
+  <si>
+    <t>D979</t>
+  </si>
+  <si>
+    <t>D980</t>
+  </si>
+  <si>
+    <t>D981</t>
+  </si>
+  <si>
+    <t>D982</t>
+  </si>
+  <si>
+    <t>D983</t>
+  </si>
+  <si>
+    <t>D984</t>
+  </si>
+  <si>
+    <t>D985</t>
+  </si>
+  <si>
+    <t>D986</t>
+  </si>
+  <si>
+    <t>D987</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4786,6 +5533,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -4807,7 +5562,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4822,6 +5577,8 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -40157,7 +40914,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14C0DDF9-E394-3A4B-9BBF-C8285CB6BEBD}">
-  <dimension ref="A1:AA873"/>
+  <dimension ref="A1:AA1046"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
@@ -58165,6 +58922,7 @@
       <c r="L386" t="s">
         <v>32</v>
       </c>
+      <c r="M386" s="8"/>
       <c r="N386" s="1" t="s">
         <v>250</v>
       </c>
@@ -64842,7 +65600,7 @@
         <v>32</v>
       </c>
       <c r="N526" s="1">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="O526" s="1">
         <v>50</v>
@@ -64971,7 +65729,7 @@
         <v>32</v>
       </c>
       <c r="N529" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O529" s="1">
         <v>20.3</v>
@@ -65033,7 +65791,7 @@
         <v>32</v>
       </c>
       <c r="N530" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O530" s="1">
         <v>3.5</v>
@@ -65412,7 +66170,7 @@
         <v>32</v>
       </c>
       <c r="N538" s="1">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="O538" s="1">
         <v>2</v>
@@ -65468,7 +66226,7 @@
         <v>32</v>
       </c>
       <c r="N539" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O539" s="1">
         <v>13</v>
@@ -65533,7 +66291,7 @@
         <v>32</v>
       </c>
       <c r="N540" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O540" s="1">
         <v>8</v>
@@ -65589,7 +66347,7 @@
         <v>32</v>
       </c>
       <c r="N541" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O541" s="1">
         <v>12</v>
@@ -65654,7 +66412,7 @@
         <v>32</v>
       </c>
       <c r="N542" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O542" s="1">
         <v>8</v>
@@ -65710,7 +66468,7 @@
         <v>32</v>
       </c>
       <c r="N543" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O543" s="1">
         <v>15</v>
@@ -65831,7 +66589,7 @@
         <v>32</v>
       </c>
       <c r="N545" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O545" s="1">
         <v>6</v>
@@ -65887,7 +66645,7 @@
         <v>32</v>
       </c>
       <c r="N546" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O546" s="1">
         <v>2.5</v>
@@ -65943,7 +66701,7 @@
         <v>32</v>
       </c>
       <c r="N547" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O547" s="1">
         <v>6</v>
@@ -65999,7 +66757,7 @@
         <v>32</v>
       </c>
       <c r="N548" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O548" s="1">
         <v>11.5</v>
@@ -66055,7 +66813,7 @@
         <v>32</v>
       </c>
       <c r="N549" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O549" s="1">
         <v>9</v>
@@ -66111,7 +66869,7 @@
         <v>32</v>
       </c>
       <c r="N550" s="1">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="O550" s="1">
         <v>9.1999999999999993</v>
@@ -66167,7 +66925,7 @@
         <v>32</v>
       </c>
       <c r="N551" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O551" s="1">
         <v>8</v>
@@ -66223,7 +66981,7 @@
         <v>32</v>
       </c>
       <c r="N552" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O552" s="1">
         <v>10</v>
@@ -66279,7 +67037,7 @@
         <v>32</v>
       </c>
       <c r="N553" s="1">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O553" s="1">
         <v>4</v>
@@ -66326,7 +67084,7 @@
         <v>32</v>
       </c>
       <c r="N554" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O554" s="1">
         <v>10</v>
@@ -66373,7 +67131,7 @@
         <v>32</v>
       </c>
       <c r="N555" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O555" s="1">
         <v>7</v>
@@ -66420,7 +67178,7 @@
         <v>32</v>
       </c>
       <c r="N556" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O556" s="1">
         <v>5</v>
@@ -66470,7 +67228,7 @@
         <v>32</v>
       </c>
       <c r="N557" s="1">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="O557" s="1">
         <v>3</v>
@@ -66516,8 +67274,9 @@
       <c r="L558" t="s">
         <v>32</v>
       </c>
+      <c r="M558" s="1"/>
       <c r="N558" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O558" s="1">
         <v>7</v>
@@ -66563,8 +67322,9 @@
       <c r="L559" t="s">
         <v>32</v>
       </c>
+      <c r="M559" s="1"/>
       <c r="N559" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O559" s="1">
         <v>5</v>
@@ -66610,8 +67370,9 @@
       <c r="L560" t="s">
         <v>32</v>
       </c>
+      <c r="M560" s="1"/>
       <c r="N560" s="1">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="O560" s="1">
         <v>4</v>
@@ -66657,8 +67418,9 @@
       <c r="L561" t="s">
         <v>32</v>
       </c>
+      <c r="M561" s="1"/>
       <c r="N561" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O561" s="1">
         <v>3</v>
@@ -66707,8 +67469,9 @@
       <c r="L562" t="s">
         <v>32</v>
       </c>
+      <c r="M562" s="1"/>
       <c r="N562" s="1">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="O562" s="1">
         <v>4</v>
@@ -66754,8 +67517,9 @@
       <c r="L563" t="s">
         <v>32</v>
       </c>
+      <c r="M563" s="1"/>
       <c r="N563" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O563" s="1">
         <v>10</v>
@@ -66804,8 +67568,9 @@
       <c r="L564" t="s">
         <v>32</v>
       </c>
+      <c r="M564" s="1"/>
       <c r="N564" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O564" s="1">
         <v>13</v>
@@ -66851,8 +67616,9 @@
       <c r="L565" t="s">
         <v>32</v>
       </c>
+      <c r="M565" s="1"/>
       <c r="N565" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O565" s="1">
         <v>8</v>
@@ -66898,8 +67664,9 @@
       <c r="L566" t="s">
         <v>32</v>
       </c>
+      <c r="M566" s="1"/>
       <c r="N566" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O566" s="1">
         <v>2</v>
@@ -66945,8 +67712,9 @@
       <c r="L567" t="s">
         <v>32</v>
       </c>
+      <c r="M567" s="1"/>
       <c r="N567" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O567" s="1">
         <v>11</v>
@@ -66992,8 +67760,9 @@
       <c r="L568" t="s">
         <v>32</v>
       </c>
+      <c r="M568" s="1"/>
       <c r="N568" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O568" s="1">
         <v>8</v>
@@ -67039,8 +67808,9 @@
       <c r="L569" t="s">
         <v>32</v>
       </c>
+      <c r="M569" s="1"/>
       <c r="N569" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O569" s="1">
         <v>13</v>
@@ -67086,8 +67856,9 @@
       <c r="L570" t="s">
         <v>32</v>
       </c>
+      <c r="M570" s="1"/>
       <c r="N570" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O570" s="1">
         <v>6</v>
@@ -67133,8 +67904,9 @@
       <c r="L571" t="s">
         <v>32</v>
       </c>
+      <c r="M571" s="1"/>
       <c r="N571" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O571" s="1">
         <v>6</v>
@@ -67180,8 +67952,9 @@
       <c r="L572" t="s">
         <v>32</v>
       </c>
+      <c r="M572" s="1"/>
       <c r="N572" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O572" s="1">
         <v>7</v>
@@ -67227,8 +68000,9 @@
       <c r="L573" t="s">
         <v>32</v>
       </c>
+      <c r="M573" s="1"/>
       <c r="N573" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O573" s="1">
         <v>6</v>
@@ -67274,8 +68048,9 @@
       <c r="L574" t="s">
         <v>32</v>
       </c>
+      <c r="M574" s="1"/>
       <c r="N574" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O574" s="1">
         <v>8</v>
@@ -67321,8 +68096,9 @@
       <c r="L575" t="s">
         <v>32</v>
       </c>
+      <c r="M575" s="1"/>
       <c r="N575" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O575" s="1">
         <v>6</v>
@@ -67368,8 +68144,9 @@
       <c r="L576" t="s">
         <v>32</v>
       </c>
+      <c r="M576" s="1"/>
       <c r="N576" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="O576" s="1">
         <v>6</v>
@@ -67415,8 +68192,9 @@
       <c r="L577" t="s">
         <v>32</v>
       </c>
+      <c r="M577" s="1"/>
       <c r="N577" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O577" s="1">
         <v>5</v>
@@ -67462,8 +68240,9 @@
       <c r="L578" t="s">
         <v>32</v>
       </c>
+      <c r="M578" s="1"/>
       <c r="N578" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O578" s="1">
         <v>6</v>
@@ -67509,8 +68288,9 @@
       <c r="L579" t="s">
         <v>32</v>
       </c>
+      <c r="M579" s="1"/>
       <c r="N579" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O579" s="1">
         <v>6</v>
@@ -67556,8 +68336,9 @@
       <c r="L580" t="s">
         <v>32</v>
       </c>
+      <c r="M580" s="1"/>
       <c r="N580" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O580" s="1">
         <v>5</v>
@@ -67603,8 +68384,9 @@
       <c r="L581" t="s">
         <v>32</v>
       </c>
+      <c r="M581" s="1"/>
       <c r="N581" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O581" s="1">
         <v>6</v>
@@ -67650,6 +68432,7 @@
       <c r="L582" t="s">
         <v>32</v>
       </c>
+      <c r="M582" s="1"/>
       <c r="N582" s="1">
         <v>3</v>
       </c>
@@ -67697,8 +68480,9 @@
       <c r="L583" t="s">
         <v>32</v>
       </c>
+      <c r="M583" s="1"/>
       <c r="N583" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O583" s="1">
         <v>12</v>
@@ -67744,6 +68528,7 @@
       <c r="L584" t="s">
         <v>32</v>
       </c>
+      <c r="M584" s="1"/>
       <c r="N584" s="1">
         <v>3</v>
       </c>
@@ -67791,6 +68576,7 @@
       <c r="L585" t="s">
         <v>32</v>
       </c>
+      <c r="M585" s="1"/>
       <c r="N585" s="1">
         <v>8</v>
       </c>
@@ -67835,6 +68621,7 @@
       <c r="L586" t="s">
         <v>32</v>
       </c>
+      <c r="M586" s="1"/>
       <c r="N586" s="1">
         <v>3</v>
       </c>
@@ -67882,6 +68669,7 @@
       <c r="L587" t="s">
         <v>32</v>
       </c>
+      <c r="M587" s="1"/>
       <c r="N587" s="1">
         <v>6</v>
       </c>
@@ -67929,6 +68717,7 @@
       <c r="L588" t="s">
         <v>32</v>
       </c>
+      <c r="M588" s="1"/>
       <c r="N588" s="1">
         <v>3</v>
       </c>
@@ -67973,6 +68762,7 @@
       <c r="L589" t="s">
         <v>32</v>
       </c>
+      <c r="M589" s="1"/>
       <c r="N589" s="1">
         <v>3</v>
       </c>
@@ -68020,6 +68810,7 @@
       <c r="L590" t="s">
         <v>32</v>
       </c>
+      <c r="M590" s="1"/>
       <c r="N590" s="1">
         <v>5</v>
       </c>
@@ -68070,6 +68861,7 @@
       <c r="L591" t="s">
         <v>32</v>
       </c>
+      <c r="M591" s="1"/>
       <c r="N591" s="1">
         <v>5</v>
       </c>
@@ -68117,6 +68909,7 @@
       <c r="L592" t="s">
         <v>32</v>
       </c>
+      <c r="M592" s="1"/>
       <c r="N592" s="1">
         <v>6</v>
       </c>
@@ -68167,6 +68960,7 @@
       <c r="L593" t="s">
         <v>32</v>
       </c>
+      <c r="M593" s="1"/>
       <c r="N593" s="1">
         <v>7</v>
       </c>
@@ -68217,6 +69011,7 @@
       <c r="L594" t="s">
         <v>32</v>
       </c>
+      <c r="M594" s="1"/>
       <c r="N594" s="1">
         <v>6</v>
       </c>
@@ -68264,6 +69059,7 @@
       <c r="L595" t="s">
         <v>32</v>
       </c>
+      <c r="M595" s="1"/>
       <c r="N595" s="1">
         <v>6</v>
       </c>
@@ -68311,6 +69107,7 @@
       <c r="L596" t="s">
         <v>32</v>
       </c>
+      <c r="M596" s="1"/>
       <c r="N596" s="1">
         <v>7</v>
       </c>
@@ -68358,6 +69155,7 @@
       <c r="L597" t="s">
         <v>32</v>
       </c>
+      <c r="M597" s="1"/>
       <c r="N597" s="1">
         <v>7</v>
       </c>
@@ -68405,6 +69203,7 @@
       <c r="L598" t="s">
         <v>32</v>
       </c>
+      <c r="M598" s="1"/>
       <c r="N598" s="1">
         <v>7</v>
       </c>
@@ -68452,6 +69251,7 @@
       <c r="L599" t="s">
         <v>32</v>
       </c>
+      <c r="M599" s="1"/>
       <c r="N599" s="1">
         <v>6</v>
       </c>
@@ -68499,6 +69299,7 @@
       <c r="L600" t="s">
         <v>32</v>
       </c>
+      <c r="M600" s="1"/>
       <c r="N600" s="1">
         <v>5</v>
       </c>
@@ -68546,6 +69347,7 @@
       <c r="L601" t="s">
         <v>32</v>
       </c>
+      <c r="M601" s="1"/>
       <c r="N601" s="1">
         <v>6</v>
       </c>
@@ -68593,6 +69395,7 @@
       <c r="L602" t="s">
         <v>32</v>
       </c>
+      <c r="M602" s="1"/>
       <c r="N602" s="1">
         <v>4</v>
       </c>
@@ -68640,6 +69443,7 @@
       <c r="L603" t="s">
         <v>32</v>
       </c>
+      <c r="M603" s="1"/>
       <c r="N603" s="1">
         <v>7</v>
       </c>
@@ -68687,6 +69491,7 @@
       <c r="L604" t="s">
         <v>32</v>
       </c>
+      <c r="M604" s="1"/>
       <c r="N604" s="1">
         <v>8</v>
       </c>
@@ -68734,6 +69539,7 @@
       <c r="L605" t="s">
         <v>32</v>
       </c>
+      <c r="M605" s="1"/>
       <c r="N605" s="1">
         <v>6</v>
       </c>
@@ -68781,6 +69587,7 @@
       <c r="L606" t="s">
         <v>32</v>
       </c>
+      <c r="M606" s="1"/>
       <c r="N606" s="1">
         <v>7</v>
       </c>
@@ -68831,6 +69638,7 @@
       <c r="L607" t="s">
         <v>32</v>
       </c>
+      <c r="M607" s="1"/>
       <c r="N607" s="1">
         <v>7</v>
       </c>
@@ -68878,6 +69686,7 @@
       <c r="L608" t="s">
         <v>32</v>
       </c>
+      <c r="M608" s="1"/>
       <c r="N608" s="1">
         <v>6</v>
       </c>
@@ -68928,6 +69737,7 @@
       <c r="L609" t="s">
         <v>32</v>
       </c>
+      <c r="M609" s="1"/>
       <c r="N609" s="1">
         <v>7</v>
       </c>
@@ -68975,6 +69785,7 @@
       <c r="L610" t="s">
         <v>32</v>
       </c>
+      <c r="M610" s="1"/>
       <c r="N610" s="1">
         <v>6</v>
       </c>
@@ -69022,6 +69833,7 @@
       <c r="L611" t="s">
         <v>32</v>
       </c>
+      <c r="M611" s="1"/>
       <c r="N611" s="1">
         <v>6</v>
       </c>
@@ -69069,6 +69881,7 @@
       <c r="L612" t="s">
         <v>32</v>
       </c>
+      <c r="M612" s="1"/>
       <c r="N612" s="1">
         <v>7</v>
       </c>
@@ -69119,6 +69932,7 @@
       <c r="L613" t="s">
         <v>32</v>
       </c>
+      <c r="M613" s="1"/>
       <c r="N613" s="1">
         <v>7</v>
       </c>
@@ -69169,6 +69983,7 @@
       <c r="L614" t="s">
         <v>32</v>
       </c>
+      <c r="M614" s="1"/>
       <c r="N614" s="1">
         <v>7</v>
       </c>
@@ -69216,6 +70031,7 @@
       <c r="L615" t="s">
         <v>32</v>
       </c>
+      <c r="M615" s="1"/>
       <c r="N615" s="1">
         <v>6</v>
       </c>
@@ -69263,6 +70079,7 @@
       <c r="L616" t="s">
         <v>32</v>
       </c>
+      <c r="M616" s="1"/>
       <c r="N616" s="1">
         <v>6</v>
       </c>
@@ -69310,6 +70127,7 @@
       <c r="L617" t="s">
         <v>32</v>
       </c>
+      <c r="M617" s="1"/>
       <c r="N617" s="1">
         <v>6</v>
       </c>
@@ -69360,6 +70178,7 @@
       <c r="L618" t="s">
         <v>32</v>
       </c>
+      <c r="M618" s="1"/>
       <c r="N618" s="1">
         <v>7</v>
       </c>
@@ -69407,6 +70226,7 @@
       <c r="L619" t="s">
         <v>32</v>
       </c>
+      <c r="M619" s="1"/>
       <c r="N619" s="1">
         <v>6</v>
       </c>
@@ -69457,6 +70277,7 @@
       <c r="L620" t="s">
         <v>32</v>
       </c>
+      <c r="M620" s="1"/>
       <c r="N620" s="1">
         <v>6</v>
       </c>
@@ -69504,6 +70325,7 @@
       <c r="L621" t="s">
         <v>32</v>
       </c>
+      <c r="M621" s="1"/>
       <c r="N621" s="1">
         <v>6</v>
       </c>
@@ -69551,6 +70373,7 @@
       <c r="L622" t="s">
         <v>32</v>
       </c>
+      <c r="M622" s="1"/>
       <c r="N622" s="1">
         <v>7</v>
       </c>
@@ -69598,6 +70421,7 @@
       <c r="L623" t="s">
         <v>32</v>
       </c>
+      <c r="M623" s="1"/>
       <c r="N623" s="1">
         <v>7</v>
       </c>
@@ -69645,6 +70469,7 @@
       <c r="L624" t="s">
         <v>32</v>
       </c>
+      <c r="M624" s="1"/>
       <c r="N624" s="1">
         <v>6</v>
       </c>
@@ -69692,6 +70517,7 @@
       <c r="L625" t="s">
         <v>32</v>
       </c>
+      <c r="M625" s="1"/>
       <c r="N625" s="1">
         <v>7</v>
       </c>
@@ -69739,6 +70565,7 @@
       <c r="L626" t="s">
         <v>32</v>
       </c>
+      <c r="M626" s="1"/>
       <c r="N626" s="1">
         <v>7</v>
       </c>
@@ -69786,6 +70613,7 @@
       <c r="L627" t="s">
         <v>32</v>
       </c>
+      <c r="M627" s="1"/>
       <c r="N627" s="1">
         <v>7</v>
       </c>
@@ -69836,6 +70664,7 @@
       <c r="L628" t="s">
         <v>32</v>
       </c>
+      <c r="M628" s="1"/>
       <c r="N628" s="1">
         <v>6</v>
       </c>
@@ -69883,6 +70712,7 @@
       <c r="L629" t="s">
         <v>32</v>
       </c>
+      <c r="M629" s="1"/>
       <c r="N629" s="1">
         <v>7</v>
       </c>
@@ -69930,6 +70760,7 @@
       <c r="L630" t="s">
         <v>32</v>
       </c>
+      <c r="M630" s="1"/>
       <c r="N630" s="1">
         <v>5</v>
       </c>
@@ -69977,6 +70808,7 @@
       <c r="L631" t="s">
         <v>32</v>
       </c>
+      <c r="M631" s="1"/>
       <c r="N631" s="1">
         <v>6</v>
       </c>
@@ -70027,6 +70859,7 @@
       <c r="L632" t="s">
         <v>32</v>
       </c>
+      <c r="M632" s="1"/>
       <c r="N632" s="1">
         <v>6</v>
       </c>
@@ -70077,6 +70910,7 @@
       <c r="L633" t="s">
         <v>32</v>
       </c>
+      <c r="M633" s="1"/>
       <c r="N633" s="1">
         <v>7</v>
       </c>
@@ -70124,6 +70958,7 @@
       <c r="L634" t="s">
         <v>32</v>
       </c>
+      <c r="M634" s="1"/>
       <c r="N634" s="1">
         <v>8</v>
       </c>
@@ -70171,6 +71006,7 @@
       <c r="L635" t="s">
         <v>32</v>
       </c>
+      <c r="M635" s="1"/>
       <c r="N635" s="1">
         <v>7</v>
       </c>
@@ -70221,6 +71057,7 @@
       <c r="L636" t="s">
         <v>32</v>
       </c>
+      <c r="M636" s="1"/>
       <c r="N636" s="1">
         <v>6</v>
       </c>
@@ -70268,6 +71105,7 @@
       <c r="L637" t="s">
         <v>32</v>
       </c>
+      <c r="M637" s="1"/>
       <c r="N637" s="1">
         <v>7</v>
       </c>
@@ -70318,6 +71156,7 @@
       <c r="L638" t="s">
         <v>32</v>
       </c>
+      <c r="M638" s="1"/>
       <c r="N638" s="1">
         <v>7</v>
       </c>
@@ -70365,6 +71204,7 @@
       <c r="L639" t="s">
         <v>32</v>
       </c>
+      <c r="M639" s="1"/>
       <c r="N639" s="1">
         <v>7</v>
       </c>
@@ -70412,6 +71252,7 @@
       <c r="L640" t="s">
         <v>32</v>
       </c>
+      <c r="M640" s="1"/>
       <c r="N640" s="1">
         <v>7</v>
       </c>
@@ -70459,6 +71300,7 @@
       <c r="L641" t="s">
         <v>32</v>
       </c>
+      <c r="M641" s="1"/>
       <c r="N641" s="1">
         <v>7</v>
       </c>
@@ -70506,6 +71348,7 @@
       <c r="L642" t="s">
         <v>32</v>
       </c>
+      <c r="M642" s="1"/>
       <c r="N642" s="1">
         <v>7</v>
       </c>
@@ -70556,6 +71399,7 @@
       <c r="L643" t="s">
         <v>32</v>
       </c>
+      <c r="M643" s="1"/>
       <c r="N643" s="1">
         <v>5</v>
       </c>
@@ -70603,6 +71447,7 @@
       <c r="L644" t="s">
         <v>32</v>
       </c>
+      <c r="M644" s="1"/>
       <c r="N644" s="1">
         <v>5</v>
       </c>
@@ -70653,6 +71498,7 @@
       <c r="L645" t="s">
         <v>32</v>
       </c>
+      <c r="M645" s="1"/>
       <c r="N645" s="1">
         <v>5</v>
       </c>
@@ -70700,6 +71546,7 @@
       <c r="L646" t="s">
         <v>32</v>
       </c>
+      <c r="M646" s="1"/>
       <c r="N646" s="1">
         <v>6</v>
       </c>
@@ -70747,6 +71594,7 @@
       <c r="L647" t="s">
         <v>32</v>
       </c>
+      <c r="M647" s="1"/>
       <c r="N647" s="1">
         <v>6</v>
       </c>
@@ -70794,6 +71642,7 @@
       <c r="L648" t="s">
         <v>32</v>
       </c>
+      <c r="M648" s="1"/>
       <c r="N648" s="1">
         <v>6</v>
       </c>
@@ -70841,6 +71690,7 @@
       <c r="L649" t="s">
         <v>32</v>
       </c>
+      <c r="M649" s="1"/>
       <c r="N649" s="1">
         <v>6</v>
       </c>
@@ -70891,6 +71741,7 @@
       <c r="L650" t="s">
         <v>32</v>
       </c>
+      <c r="M650" s="1"/>
       <c r="N650" s="1">
         <v>6</v>
       </c>
@@ -70941,6 +71792,7 @@
       <c r="L651" t="s">
         <v>32</v>
       </c>
+      <c r="M651" s="1"/>
       <c r="N651" s="1">
         <v>5</v>
       </c>
@@ -70988,6 +71840,7 @@
       <c r="L652" t="s">
         <v>32</v>
       </c>
+      <c r="M652" s="1"/>
       <c r="N652" s="1">
         <v>7</v>
       </c>
@@ -71035,6 +71888,7 @@
       <c r="L653" t="s">
         <v>32</v>
       </c>
+      <c r="M653" s="1"/>
       <c r="N653" s="1">
         <v>7</v>
       </c>
@@ -71082,6 +71936,7 @@
       <c r="L654" t="s">
         <v>32</v>
       </c>
+      <c r="M654" s="1"/>
       <c r="N654" s="1">
         <v>7</v>
       </c>
@@ -71129,6 +71984,7 @@
       <c r="L655" t="s">
         <v>32</v>
       </c>
+      <c r="M655" s="1"/>
       <c r="N655" s="1">
         <v>6</v>
       </c>
@@ -71176,6 +72032,7 @@
       <c r="L656" t="s">
         <v>32</v>
       </c>
+      <c r="M656" s="1"/>
       <c r="N656" s="1">
         <v>6</v>
       </c>
@@ -71223,6 +72080,7 @@
       <c r="L657" t="s">
         <v>32</v>
       </c>
+      <c r="M657" s="1"/>
       <c r="N657" s="1">
         <v>7</v>
       </c>
@@ -71270,6 +72128,7 @@
       <c r="L658" t="s">
         <v>32</v>
       </c>
+      <c r="M658" s="1"/>
       <c r="N658" s="1">
         <v>7</v>
       </c>
@@ -71317,6 +72176,7 @@
       <c r="L659" t="s">
         <v>32</v>
       </c>
+      <c r="M659" s="1"/>
       <c r="N659" s="1">
         <v>6</v>
       </c>
@@ -71364,6 +72224,7 @@
       <c r="L660" t="s">
         <v>32</v>
       </c>
+      <c r="M660" s="1"/>
       <c r="N660" s="1">
         <v>7</v>
       </c>
@@ -71408,6 +72269,7 @@
       <c r="L661" t="s">
         <v>32</v>
       </c>
+      <c r="M661" s="1"/>
       <c r="N661" s="1">
         <v>6</v>
       </c>
@@ -71452,6 +72314,7 @@
       <c r="L662" t="s">
         <v>32</v>
       </c>
+      <c r="M662" s="1"/>
       <c r="N662" s="1">
         <v>7</v>
       </c>
@@ -71499,6 +72362,7 @@
       <c r="L663" t="s">
         <v>32</v>
       </c>
+      <c r="M663" s="1"/>
       <c r="N663" s="1">
         <v>5</v>
       </c>
@@ -71543,6 +72407,7 @@
       <c r="L664" t="s">
         <v>32</v>
       </c>
+      <c r="M664" s="1"/>
       <c r="N664" s="1">
         <v>6</v>
       </c>
@@ -71587,6 +72452,7 @@
       <c r="L665" t="s">
         <v>32</v>
       </c>
+      <c r="M665" s="1"/>
       <c r="N665" s="1">
         <v>6</v>
       </c>
@@ -71631,6 +72497,7 @@
       <c r="L666" t="s">
         <v>32</v>
       </c>
+      <c r="M666" s="1"/>
       <c r="O666" s="1">
         <v>4</v>
       </c>
@@ -71669,6 +72536,7 @@
       <c r="L667" t="s">
         <v>32</v>
       </c>
+      <c r="M667" s="1"/>
       <c r="N667" s="1">
         <v>3</v>
       </c>
@@ -71713,6 +72581,7 @@
       <c r="L668" t="s">
         <v>32</v>
       </c>
+      <c r="M668" s="1"/>
       <c r="N668" s="1">
         <v>6</v>
       </c>
@@ -71757,6 +72626,7 @@
       <c r="L669" t="s">
         <v>32</v>
       </c>
+      <c r="M669" s="1"/>
       <c r="N669" s="1">
         <v>7</v>
       </c>
@@ -71804,6 +72674,7 @@
       <c r="L670" t="s">
         <v>32</v>
       </c>
+      <c r="M670" s="1"/>
       <c r="N670" s="1">
         <v>7</v>
       </c>
@@ -71848,6 +72719,7 @@
       <c r="L671" t="s">
         <v>32</v>
       </c>
+      <c r="M671" s="1"/>
       <c r="N671" s="1">
         <v>8</v>
       </c>
@@ -71892,6 +72764,7 @@
       <c r="L672" t="s">
         <v>32</v>
       </c>
+      <c r="M672" s="1"/>
       <c r="N672" s="1">
         <v>6</v>
       </c>
@@ -71936,6 +72809,7 @@
       <c r="L673" t="s">
         <v>32</v>
       </c>
+      <c r="M673" s="1"/>
       <c r="N673" s="1">
         <v>7</v>
       </c>
@@ -71980,6 +72854,7 @@
       <c r="L674" t="s">
         <v>32</v>
       </c>
+      <c r="M674" s="1"/>
       <c r="N674" s="1">
         <v>6</v>
       </c>
@@ -72018,12 +72893,16 @@
       <c r="H675" t="s">
         <v>30</v>
       </c>
+      <c r="J675" t="s">
+        <v>77</v>
+      </c>
       <c r="K675" t="s">
         <v>1472</v>
       </c>
       <c r="L675" t="s">
         <v>32</v>
       </c>
+      <c r="M675" s="1"/>
       <c r="N675" s="1">
         <v>6</v>
       </c>
@@ -72071,6 +72950,7 @@
       <c r="L676" t="s">
         <v>32</v>
       </c>
+      <c r="M676" s="1"/>
       <c r="N676" s="1">
         <v>5</v>
       </c>
@@ -72118,6 +72998,7 @@
       <c r="L677" t="s">
         <v>32</v>
       </c>
+      <c r="M677" s="1"/>
       <c r="N677" s="1">
         <v>6</v>
       </c>
@@ -72165,6 +73046,7 @@
       <c r="L678" t="s">
         <v>32</v>
       </c>
+      <c r="M678" s="1"/>
       <c r="N678" s="1">
         <v>6</v>
       </c>
@@ -72209,6 +73091,7 @@
       <c r="L679" t="s">
         <v>32</v>
       </c>
+      <c r="M679" s="1"/>
       <c r="N679" s="1">
         <v>6</v>
       </c>
@@ -72253,6 +73136,7 @@
       <c r="L680" t="s">
         <v>32</v>
       </c>
+      <c r="M680" s="1"/>
       <c r="N680" s="1">
         <v>7</v>
       </c>
@@ -72294,6 +73178,7 @@
       <c r="L681" t="s">
         <v>32</v>
       </c>
+      <c r="M681" s="1"/>
       <c r="N681" s="1">
         <v>7</v>
       </c>
@@ -72332,6 +73217,7 @@
       <c r="L682" t="s">
         <v>32</v>
       </c>
+      <c r="M682" s="1"/>
       <c r="N682" s="1">
         <v>4</v>
       </c>
@@ -72371,6 +73257,7 @@
       <c r="L683" t="s">
         <v>32</v>
       </c>
+      <c r="M683" s="1"/>
       <c r="N683" s="1">
         <v>3</v>
       </c>
@@ -72418,6 +73305,7 @@
       <c r="L684" t="s">
         <v>32</v>
       </c>
+      <c r="M684" s="1"/>
       <c r="N684" s="1">
         <v>4</v>
       </c>
@@ -72462,6 +73350,7 @@
       <c r="L685" t="s">
         <v>32</v>
       </c>
+      <c r="M685" s="1"/>
       <c r="N685" s="1">
         <v>7</v>
       </c>
@@ -72506,6 +73395,7 @@
       <c r="L686" t="s">
         <v>32</v>
       </c>
+      <c r="M686" s="1"/>
       <c r="N686" s="1">
         <v>6</v>
       </c>
@@ -72550,6 +73440,7 @@
       <c r="L687" t="s">
         <v>32</v>
       </c>
+      <c r="M687" s="1"/>
       <c r="N687" s="1">
         <v>7</v>
       </c>
@@ -72594,6 +73485,7 @@
       <c r="L688" t="s">
         <v>32</v>
       </c>
+      <c r="M688" s="1"/>
       <c r="N688" s="1">
         <v>6</v>
       </c>
@@ -72638,6 +73530,7 @@
       <c r="L689" t="s">
         <v>32</v>
       </c>
+      <c r="M689" s="1"/>
       <c r="N689" s="1">
         <v>6</v>
       </c>
@@ -72685,8 +73578,9 @@
       <c r="L690" t="s">
         <v>32</v>
       </c>
+      <c r="M690" s="1"/>
       <c r="N690" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O690" s="1">
         <v>17</v>
@@ -72729,8 +73623,9 @@
       <c r="L691" t="s">
         <v>32</v>
       </c>
+      <c r="M691" s="1"/>
       <c r="N691" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O691" s="1">
         <v>12</v>
@@ -72773,8 +73668,9 @@
       <c r="L692" t="s">
         <v>32</v>
       </c>
+      <c r="M692" s="1"/>
       <c r="N692" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O692" s="1">
         <v>15</v>
@@ -72817,8 +73713,9 @@
       <c r="L693" t="s">
         <v>32</v>
       </c>
+      <c r="M693" s="1"/>
       <c r="N693" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O693" s="1">
         <v>10</v>
@@ -72861,8 +73758,9 @@
       <c r="L694" t="s">
         <v>32</v>
       </c>
+      <c r="M694" s="1"/>
       <c r="N694" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O694" s="1">
         <v>8</v>
@@ -72905,8 +73803,9 @@
       <c r="L695" t="s">
         <v>32</v>
       </c>
+      <c r="M695" s="1"/>
       <c r="N695" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O695" s="1">
         <v>12</v>
@@ -72949,8 +73848,9 @@
       <c r="L696" t="s">
         <v>32</v>
       </c>
+      <c r="M696" s="1"/>
       <c r="N696" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O696" s="1">
         <v>7</v>
@@ -72993,8 +73893,9 @@
       <c r="L697" t="s">
         <v>32</v>
       </c>
+      <c r="M697" s="1"/>
       <c r="N697" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O697" s="1">
         <v>4</v>
@@ -73037,8 +73938,9 @@
       <c r="L698" t="s">
         <v>32</v>
       </c>
+      <c r="M698" s="1"/>
       <c r="N698" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O698" s="1">
         <v>5</v>
@@ -73084,8 +73986,9 @@
       <c r="L699" t="s">
         <v>32</v>
       </c>
+      <c r="M699" s="1"/>
       <c r="N699" s="1">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="O699" s="1">
         <v>3</v>
@@ -73128,8 +74031,9 @@
       <c r="L700" t="s">
         <v>32</v>
       </c>
+      <c r="M700" s="1"/>
       <c r="N700" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O700" s="1">
         <v>10</v>
@@ -73172,8 +74076,9 @@
       <c r="L701" t="s">
         <v>32</v>
       </c>
+      <c r="M701" s="1"/>
       <c r="N701" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O701" s="1">
         <v>3</v>
@@ -73219,6 +74124,7 @@
       <c r="L702" t="s">
         <v>32</v>
       </c>
+      <c r="M702" s="1"/>
       <c r="O702" s="1">
         <v>3</v>
       </c>
@@ -73260,8 +74166,9 @@
       <c r="L703" t="s">
         <v>32</v>
       </c>
+      <c r="M703" s="1"/>
       <c r="N703" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O703" s="1">
         <v>6</v>
@@ -73304,8 +74211,9 @@
       <c r="L704" t="s">
         <v>32</v>
       </c>
+      <c r="M704" s="1"/>
       <c r="N704" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O704" s="1">
         <v>5</v>
@@ -73348,8 +74256,9 @@
       <c r="L705" t="s">
         <v>32</v>
       </c>
+      <c r="M705" s="1"/>
       <c r="N705" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O705" s="1">
         <v>4</v>
@@ -73392,8 +74301,9 @@
       <c r="L706" t="s">
         <v>32</v>
       </c>
+      <c r="M706" s="1"/>
       <c r="N706" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O706" s="1">
         <v>5.5</v>
@@ -73436,6 +74346,7 @@
       <c r="L707" t="s">
         <v>32</v>
       </c>
+      <c r="M707" s="1"/>
       <c r="O707" s="1">
         <v>3.5</v>
       </c>
@@ -73477,8 +74388,9 @@
       <c r="L708" t="s">
         <v>32</v>
       </c>
+      <c r="M708" s="1"/>
       <c r="N708" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O708" s="1">
         <v>13</v>
@@ -73521,8 +74433,9 @@
       <c r="L709" t="s">
         <v>32</v>
       </c>
+      <c r="M709" s="1"/>
       <c r="N709" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O709" s="1">
         <v>5</v>
@@ -73568,8 +74481,9 @@
       <c r="L710" t="s">
         <v>32</v>
       </c>
+      <c r="M710" s="1"/>
       <c r="N710" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O710" s="1">
         <v>14</v>
@@ -73612,8 +74526,9 @@
       <c r="L711" t="s">
         <v>32</v>
       </c>
+      <c r="M711" s="1"/>
       <c r="N711" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O711" s="1">
         <v>8</v>
@@ -73656,8 +74571,9 @@
       <c r="L712" t="s">
         <v>32</v>
       </c>
+      <c r="M712" s="1"/>
       <c r="N712" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O712" s="1">
         <v>6</v>
@@ -73700,8 +74616,9 @@
       <c r="L713" t="s">
         <v>32</v>
       </c>
+      <c r="M713" s="1"/>
       <c r="N713" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O713" s="1">
         <v>3.5</v>
@@ -73744,8 +74661,9 @@
       <c r="L714" t="s">
         <v>32</v>
       </c>
+      <c r="M714" s="1"/>
       <c r="N714" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O714" s="1">
         <v>15</v>
@@ -73788,8 +74706,9 @@
       <c r="L715" t="s">
         <v>32</v>
       </c>
+      <c r="M715" s="1"/>
       <c r="N715" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O715" s="1">
         <v>4</v>
@@ -73832,6 +74751,7 @@
       <c r="L716" t="s">
         <v>32</v>
       </c>
+      <c r="M716" s="1"/>
       <c r="N716" s="1">
         <v>6</v>
       </c>
@@ -73879,6 +74799,7 @@
       <c r="L717" t="s">
         <v>32</v>
       </c>
+      <c r="M717" s="1"/>
       <c r="N717" s="1">
         <v>5</v>
       </c>
@@ -79209,7 +80130,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="849" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A849" t="s">
         <v>1530</v>
       </c>
@@ -79250,7 +80171,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="850" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A850" t="s">
         <v>1531</v>
       </c>
@@ -79288,7 +80209,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="851" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A851" t="s">
         <v>1532</v>
       </c>
@@ -79323,7 +80244,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="852" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A852" t="s">
         <v>1533</v>
       </c>
@@ -79361,7 +80282,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="853" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A853" t="s">
         <v>1534</v>
       </c>
@@ -79399,7 +80320,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="854" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A854" t="s">
         <v>1535</v>
       </c>
@@ -79437,7 +80358,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="855" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A855" t="s">
         <v>1536</v>
       </c>
@@ -79475,7 +80396,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="856" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A856" t="s">
         <v>1537</v>
       </c>
@@ -79513,7 +80434,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="857" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A857" t="s">
         <v>1538</v>
       </c>
@@ -79545,126 +80466,6218 @@
         <v>12</v>
       </c>
     </row>
-    <row r="858" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A858" t="s">
         <v>1539</v>
       </c>
+      <c r="B858" s="2">
+        <v>45074</v>
+      </c>
       <c r="C858" t="s">
         <v>114</v>
       </c>
+      <c r="D858">
+        <v>1</v>
+      </c>
+      <c r="E858" t="s">
+        <v>54</v>
+      </c>
+      <c r="F858" t="s">
+        <v>1477</v>
+      </c>
+      <c r="G858" t="s">
+        <v>65</v>
+      </c>
+      <c r="H858" t="s">
+        <v>1483</v>
+      </c>
+      <c r="J858" t="s">
+        <v>54</v>
+      </c>
+      <c r="K858" t="s">
+        <v>1568</v>
+      </c>
       <c r="L858" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="859" spans="1:18" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+      <c r="N858" s="1">
+        <v>3</v>
+      </c>
+      <c r="O858" s="1">
+        <v>10</v>
+      </c>
+      <c r="P858" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="859" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A859" t="s">
         <v>1540</v>
       </c>
+      <c r="B859" s="2">
+        <v>45075</v>
+      </c>
       <c r="C859" t="s">
         <v>114</v>
       </c>
+      <c r="D859">
+        <v>1</v>
+      </c>
+      <c r="E859" t="s">
+        <v>54</v>
+      </c>
+      <c r="F859" t="s">
+        <v>1500</v>
+      </c>
+      <c r="G859" t="s">
+        <v>65</v>
+      </c>
+      <c r="H859" t="s">
+        <v>1569</v>
+      </c>
+      <c r="J859" t="s">
+        <v>54</v>
+      </c>
+      <c r="K859" t="s">
+        <v>1568</v>
+      </c>
       <c r="L859" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="860" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="N859" s="1">
+        <v>2</v>
+      </c>
+      <c r="O859" s="1">
+        <v>8</v>
+      </c>
+      <c r="P859" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="860" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A860" t="s">
         <v>1541</v>
       </c>
+      <c r="B860" s="2">
+        <v>45079</v>
+      </c>
       <c r="C860" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="861" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="D860">
+        <v>1</v>
+      </c>
+      <c r="E860" t="s">
+        <v>54</v>
+      </c>
+      <c r="F860" t="s">
+        <v>1505</v>
+      </c>
+      <c r="G860" t="s">
+        <v>65</v>
+      </c>
+      <c r="H860" t="s">
+        <v>1569</v>
+      </c>
+      <c r="J860" t="s">
+        <v>54</v>
+      </c>
+      <c r="K860" t="s">
+        <v>1568</v>
+      </c>
+      <c r="L860" t="s">
+        <v>32</v>
+      </c>
+      <c r="N860" s="1">
+        <v>2</v>
+      </c>
+      <c r="O860" s="1">
+        <v>10</v>
+      </c>
+      <c r="P860" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="861" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A861" t="s">
         <v>1542</v>
       </c>
+      <c r="B861" s="2">
+        <v>45082</v>
+      </c>
       <c r="C861" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="862" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="D861">
+        <v>1</v>
+      </c>
+      <c r="E861" t="s">
+        <v>54</v>
+      </c>
+      <c r="F861" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G861" t="s">
+        <v>111</v>
+      </c>
+      <c r="H861" t="s">
+        <v>1569</v>
+      </c>
+      <c r="J861" t="s">
+        <v>54</v>
+      </c>
+      <c r="K861" t="s">
+        <v>1568</v>
+      </c>
+      <c r="L861" t="s">
+        <v>32</v>
+      </c>
+      <c r="N861" s="1">
+        <v>1</v>
+      </c>
+      <c r="O861" s="1">
+        <v>3</v>
+      </c>
+      <c r="P861" t="s">
+        <v>35</v>
+      </c>
+      <c r="T861" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="862" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A862" t="s">
         <v>1543</v>
       </c>
+      <c r="B862" s="2">
+        <v>45082</v>
+      </c>
       <c r="C862" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="863" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="D862">
+        <v>1</v>
+      </c>
+      <c r="E862" t="s">
+        <v>54</v>
+      </c>
+      <c r="F862" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G862" t="s">
+        <v>29</v>
+      </c>
+      <c r="H862" t="s">
+        <v>245</v>
+      </c>
+      <c r="J862" t="s">
+        <v>54</v>
+      </c>
+      <c r="K862" t="s">
+        <v>1568</v>
+      </c>
+      <c r="L862" t="s">
+        <v>45</v>
+      </c>
+      <c r="N862" s="1">
+        <v>3</v>
+      </c>
+      <c r="O862" s="1">
+        <v>10</v>
+      </c>
+      <c r="P862" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="863" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A863" t="s">
         <v>1544</v>
       </c>
+      <c r="B863" s="2">
+        <v>45086</v>
+      </c>
       <c r="C863" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="864" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="D863">
+        <v>1</v>
+      </c>
+      <c r="E863" t="s">
+        <v>54</v>
+      </c>
+      <c r="F863" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G863" t="s">
+        <v>29</v>
+      </c>
+      <c r="H863" t="s">
+        <v>245</v>
+      </c>
+      <c r="J863" t="s">
+        <v>54</v>
+      </c>
+      <c r="K863" t="s">
+        <v>1568</v>
+      </c>
+      <c r="L863" t="s">
+        <v>45</v>
+      </c>
+      <c r="O863" s="1">
+        <v>8</v>
+      </c>
+      <c r="P863" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="864" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A864" t="s">
         <v>1545</v>
       </c>
+      <c r="B864" s="2">
+        <v>45098</v>
+      </c>
       <c r="C864" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="865" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D864">
+        <v>1</v>
+      </c>
+      <c r="E864" t="s">
+        <v>54</v>
+      </c>
+      <c r="F864" t="s">
+        <v>783</v>
+      </c>
+      <c r="G864" t="s">
+        <v>29</v>
+      </c>
+      <c r="J864" t="s">
+        <v>54</v>
+      </c>
+      <c r="K864" t="s">
+        <v>1571</v>
+      </c>
+      <c r="L864" t="s">
+        <v>32</v>
+      </c>
+      <c r="N864" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O864" s="1">
+        <v>5</v>
+      </c>
+      <c r="P864" t="s">
+        <v>89</v>
+      </c>
+      <c r="R864">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="865" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A865" t="s">
         <v>1546</v>
       </c>
+      <c r="B865" s="2">
+        <v>45099</v>
+      </c>
       <c r="C865" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="866" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D865">
+        <v>1</v>
+      </c>
+      <c r="E865" t="s">
+        <v>54</v>
+      </c>
+      <c r="F865" t="s">
+        <v>783</v>
+      </c>
+      <c r="G865" t="s">
+        <v>29</v>
+      </c>
+      <c r="J865" t="s">
+        <v>54</v>
+      </c>
+      <c r="K865" t="s">
+        <v>1571</v>
+      </c>
+      <c r="L865" t="s">
+        <v>32</v>
+      </c>
+      <c r="N865" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="O865" s="1">
+        <v>2</v>
+      </c>
+      <c r="P865" t="s">
+        <v>89</v>
+      </c>
+      <c r="R865">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="866" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A866" t="s">
         <v>1547</v>
       </c>
+      <c r="B866" s="2">
+        <v>45100</v>
+      </c>
       <c r="C866" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="867" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D866">
+        <v>1</v>
+      </c>
+      <c r="E866" t="s">
+        <v>54</v>
+      </c>
+      <c r="F866" t="s">
+        <v>783</v>
+      </c>
+      <c r="G866" t="s">
+        <v>29</v>
+      </c>
+      <c r="J866" t="s">
+        <v>54</v>
+      </c>
+      <c r="K866" t="s">
+        <v>1571</v>
+      </c>
+      <c r="L866" t="s">
+        <v>32</v>
+      </c>
+      <c r="N866" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="O866" s="1">
+        <v>3</v>
+      </c>
+      <c r="P866" t="s">
+        <v>89</v>
+      </c>
+      <c r="R866">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="867" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A867" t="s">
         <v>1560</v>
       </c>
+      <c r="B867" s="2">
+        <v>45100</v>
+      </c>
       <c r="C867" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="868" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D867">
+        <v>1</v>
+      </c>
+      <c r="E867" t="s">
+        <v>54</v>
+      </c>
+      <c r="F867" t="s">
+        <v>783</v>
+      </c>
+      <c r="G867" t="s">
+        <v>29</v>
+      </c>
+      <c r="J867" t="s">
+        <v>54</v>
+      </c>
+      <c r="K867" t="s">
+        <v>1571</v>
+      </c>
+      <c r="L867" t="s">
+        <v>32</v>
+      </c>
+      <c r="N867" s="1">
+        <v>1</v>
+      </c>
+      <c r="O867" s="1">
+        <v>5</v>
+      </c>
+      <c r="P867" t="s">
+        <v>89</v>
+      </c>
+      <c r="R867">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="868" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A868" t="s">
         <v>1561</v>
       </c>
+      <c r="B868" s="2">
+        <v>45108</v>
+      </c>
       <c r="C868" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="869" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D868">
+        <v>1</v>
+      </c>
+      <c r="E868" t="s">
+        <v>54</v>
+      </c>
+      <c r="F868" t="s">
+        <v>783</v>
+      </c>
+      <c r="G868" t="s">
+        <v>29</v>
+      </c>
+      <c r="J868" t="s">
+        <v>54</v>
+      </c>
+      <c r="K868" t="s">
+        <v>1571</v>
+      </c>
+      <c r="L868" t="s">
+        <v>32</v>
+      </c>
+      <c r="N868" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="O868" s="1">
+        <v>2</v>
+      </c>
+      <c r="P868" t="s">
+        <v>35</v>
+      </c>
+      <c r="R868">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="869" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A869" t="s">
         <v>1562</v>
       </c>
+      <c r="B869" s="2">
+        <v>45109</v>
+      </c>
       <c r="C869" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="870" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D869">
+        <v>1</v>
+      </c>
+      <c r="E869" t="s">
+        <v>54</v>
+      </c>
+      <c r="F869" t="s">
+        <v>783</v>
+      </c>
+      <c r="G869" t="s">
+        <v>29</v>
+      </c>
+      <c r="J869" t="s">
+        <v>54</v>
+      </c>
+      <c r="K869" t="s">
+        <v>1571</v>
+      </c>
+      <c r="L869" t="s">
+        <v>32</v>
+      </c>
+      <c r="N869" s="1">
+        <v>1</v>
+      </c>
+      <c r="O869" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="P869" t="s">
+        <v>35</v>
+      </c>
+      <c r="R869">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="870" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A870" t="s">
         <v>1563</v>
       </c>
-    </row>
-    <row r="871" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B870" s="2">
+        <v>45114</v>
+      </c>
+      <c r="C870" t="s">
+        <v>114</v>
+      </c>
+      <c r="D870">
+        <v>1</v>
+      </c>
+      <c r="E870" t="s">
+        <v>54</v>
+      </c>
+      <c r="F870" t="s">
+        <v>783</v>
+      </c>
+      <c r="G870" t="s">
+        <v>29</v>
+      </c>
+      <c r="J870" t="s">
+        <v>54</v>
+      </c>
+      <c r="K870" t="s">
+        <v>1571</v>
+      </c>
+      <c r="L870" t="s">
+        <v>32</v>
+      </c>
+      <c r="N870" s="1">
+        <v>1</v>
+      </c>
+      <c r="O870" s="1">
+        <v>4</v>
+      </c>
+      <c r="P870" t="s">
+        <v>35</v>
+      </c>
+      <c r="R870">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="871" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A871" t="s">
         <v>1564</v>
       </c>
-    </row>
-    <row r="872" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B871" s="2">
+        <v>45126</v>
+      </c>
+      <c r="C871" t="s">
+        <v>114</v>
+      </c>
+      <c r="D871">
+        <v>1</v>
+      </c>
+      <c r="E871" t="s">
+        <v>54</v>
+      </c>
+      <c r="F871" t="s">
+        <v>783</v>
+      </c>
+      <c r="G871" t="s">
+        <v>29</v>
+      </c>
+      <c r="J871" t="s">
+        <v>54</v>
+      </c>
+      <c r="K871" t="s">
+        <v>1571</v>
+      </c>
+      <c r="L871" t="s">
+        <v>32</v>
+      </c>
+      <c r="N871" s="1">
+        <v>2</v>
+      </c>
+      <c r="O871" s="1">
+        <v>1</v>
+      </c>
+      <c r="P871" t="s">
+        <v>35</v>
+      </c>
+      <c r="R871">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="872" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A872" t="s">
         <v>1565</v>
       </c>
-    </row>
-    <row r="873" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B872" s="2">
+        <v>45099</v>
+      </c>
+      <c r="C872" t="s">
+        <v>114</v>
+      </c>
+      <c r="D872">
+        <v>1</v>
+      </c>
+      <c r="E872" t="s">
+        <v>37</v>
+      </c>
+      <c r="F872" t="s">
+        <v>1550</v>
+      </c>
+      <c r="G872" t="s">
+        <v>65</v>
+      </c>
+      <c r="J872" t="s">
+        <v>54</v>
+      </c>
+      <c r="K872" t="s">
+        <v>1572</v>
+      </c>
+      <c r="L872" t="s">
+        <v>32</v>
+      </c>
+      <c r="N872" s="1">
+        <v>3</v>
+      </c>
+      <c r="O872" s="1">
+        <v>2</v>
+      </c>
+      <c r="P872" t="s">
+        <v>89</v>
+      </c>
+      <c r="R872">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="873" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A873" t="s">
         <v>1566</v>
+      </c>
+      <c r="B873" s="2">
+        <v>45114</v>
+      </c>
+      <c r="C873" t="s">
+        <v>114</v>
+      </c>
+      <c r="D873">
+        <v>1</v>
+      </c>
+      <c r="E873" t="s">
+        <v>37</v>
+      </c>
+      <c r="F873" t="s">
+        <v>1550</v>
+      </c>
+      <c r="G873" t="s">
+        <v>65</v>
+      </c>
+      <c r="J873" t="s">
+        <v>54</v>
+      </c>
+      <c r="K873" t="s">
+        <v>415</v>
+      </c>
+      <c r="L873" t="s">
+        <v>32</v>
+      </c>
+      <c r="N873" s="1">
+        <v>3</v>
+      </c>
+      <c r="O873" s="1">
+        <v>5</v>
+      </c>
+      <c r="P873" t="s">
+        <v>89</v>
+      </c>
+      <c r="R873">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="874" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A874" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B874" s="2">
+        <v>45126</v>
+      </c>
+      <c r="C874" t="s">
+        <v>114</v>
+      </c>
+      <c r="D874">
+        <v>1</v>
+      </c>
+      <c r="E874" t="s">
+        <v>37</v>
+      </c>
+      <c r="F874" t="s">
+        <v>1550</v>
+      </c>
+      <c r="G874" t="s">
+        <v>65</v>
+      </c>
+      <c r="J874" t="s">
+        <v>54</v>
+      </c>
+      <c r="K874" t="s">
+        <v>1572</v>
+      </c>
+      <c r="L874" t="s">
+        <v>32</v>
+      </c>
+      <c r="N874" s="1">
+        <v>3</v>
+      </c>
+      <c r="O874" s="1">
+        <v>4</v>
+      </c>
+      <c r="P874" t="s">
+        <v>89</v>
+      </c>
+      <c r="R874">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="875" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A875" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B875" s="2">
+        <v>45090</v>
+      </c>
+      <c r="C875" t="s">
+        <v>114</v>
+      </c>
+      <c r="D875">
+        <v>1</v>
+      </c>
+      <c r="E875" t="s">
+        <v>37</v>
+      </c>
+      <c r="F875" t="s">
+        <v>1575</v>
+      </c>
+      <c r="G875" t="s">
+        <v>111</v>
+      </c>
+      <c r="J875" t="s">
+        <v>54</v>
+      </c>
+      <c r="K875" t="s">
+        <v>1571</v>
+      </c>
+      <c r="N875" s="1">
+        <v>120</v>
+      </c>
+      <c r="O875" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P875" t="s">
+        <v>89</v>
+      </c>
+      <c r="R875">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="876" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A876" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B876" s="2">
+        <v>45112</v>
+      </c>
+      <c r="C876" t="s">
+        <v>114</v>
+      </c>
+      <c r="D876">
+        <v>1</v>
+      </c>
+      <c r="E876" t="s">
+        <v>37</v>
+      </c>
+      <c r="F876" t="s">
+        <v>1575</v>
+      </c>
+      <c r="G876" t="s">
+        <v>111</v>
+      </c>
+      <c r="J876" t="s">
+        <v>54</v>
+      </c>
+      <c r="K876" t="s">
+        <v>1571</v>
+      </c>
+      <c r="N876" s="1">
+        <v>120</v>
+      </c>
+      <c r="O876" s="1">
+        <v>200</v>
+      </c>
+      <c r="P876" t="s">
+        <v>89</v>
+      </c>
+      <c r="R876">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="877" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A877" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B877" s="2">
+        <v>45117</v>
+      </c>
+      <c r="C877" t="s">
+        <v>114</v>
+      </c>
+      <c r="D877">
+        <v>1</v>
+      </c>
+      <c r="E877" t="s">
+        <v>37</v>
+      </c>
+      <c r="F877" t="s">
+        <v>1575</v>
+      </c>
+      <c r="G877" t="s">
+        <v>111</v>
+      </c>
+      <c r="J877" t="s">
+        <v>54</v>
+      </c>
+      <c r="K877" t="s">
+        <v>1571</v>
+      </c>
+      <c r="N877" s="1">
+        <v>120</v>
+      </c>
+      <c r="O877" s="1">
+        <v>300</v>
+      </c>
+      <c r="P877" t="s">
+        <v>89</v>
+      </c>
+      <c r="R877">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="878" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A878" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B878" s="2">
+        <v>45081</v>
+      </c>
+      <c r="C878" t="s">
+        <v>114</v>
+      </c>
+      <c r="D878">
+        <v>1</v>
+      </c>
+      <c r="E878" t="s">
+        <v>59</v>
+      </c>
+      <c r="F878" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G878" t="s">
+        <v>29</v>
+      </c>
+      <c r="J878" t="s">
+        <v>249</v>
+      </c>
+      <c r="L878" t="s">
+        <v>32</v>
+      </c>
+      <c r="N878" s="1">
+        <v>7</v>
+      </c>
+      <c r="O878" s="1">
+        <v>17</v>
+      </c>
+      <c r="P878" t="s">
+        <v>89</v>
+      </c>
+      <c r="R878">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="879" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A879" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B879" s="2">
+        <v>45087</v>
+      </c>
+      <c r="C879" t="s">
+        <v>114</v>
+      </c>
+      <c r="D879">
+        <v>1</v>
+      </c>
+      <c r="E879" t="s">
+        <v>59</v>
+      </c>
+      <c r="F879" t="s">
+        <v>1581</v>
+      </c>
+      <c r="G879" t="s">
+        <v>29</v>
+      </c>
+      <c r="J879" t="s">
+        <v>249</v>
+      </c>
+      <c r="L879" t="s">
+        <v>32</v>
+      </c>
+      <c r="N879" s="1">
+        <v>8</v>
+      </c>
+      <c r="O879" s="1">
+        <v>20</v>
+      </c>
+      <c r="P879" t="s">
+        <v>89</v>
+      </c>
+      <c r="R879">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="880" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A880" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B880" s="2">
+        <v>45091</v>
+      </c>
+      <c r="C880" t="s">
+        <v>114</v>
+      </c>
+      <c r="D880">
+        <v>1</v>
+      </c>
+      <c r="E880" t="s">
+        <v>59</v>
+      </c>
+      <c r="F880" t="s">
+        <v>1583</v>
+      </c>
+      <c r="G880" t="s">
+        <v>65</v>
+      </c>
+      <c r="J880" t="s">
+        <v>59</v>
+      </c>
+      <c r="L880" t="s">
+        <v>45</v>
+      </c>
+      <c r="N880" s="1">
+        <v>3</v>
+      </c>
+      <c r="O880" s="1">
+        <v>10</v>
+      </c>
+      <c r="P880" t="s">
+        <v>35</v>
+      </c>
+      <c r="R880">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="881" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A881" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B881" s="2">
+        <v>45096</v>
+      </c>
+      <c r="C881" t="s">
+        <v>114</v>
+      </c>
+      <c r="D881">
+        <v>1</v>
+      </c>
+      <c r="E881" t="s">
+        <v>59</v>
+      </c>
+      <c r="F881" t="s">
+        <v>1585</v>
+      </c>
+      <c r="G881" t="s">
+        <v>65</v>
+      </c>
+      <c r="J881" t="s">
+        <v>59</v>
+      </c>
+      <c r="L881" t="s">
+        <v>32</v>
+      </c>
+      <c r="N881" s="1">
+        <v>5</v>
+      </c>
+      <c r="O881" s="1">
+        <v>8</v>
+      </c>
+      <c r="P881" t="s">
+        <v>35</v>
+      </c>
+      <c r="R881">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="882" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A882" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B882" s="2">
+        <v>45105</v>
+      </c>
+      <c r="C882" t="s">
+        <v>114</v>
+      </c>
+      <c r="D882">
+        <v>1</v>
+      </c>
+      <c r="E882" t="s">
+        <v>59</v>
+      </c>
+      <c r="F882" t="s">
+        <v>1587</v>
+      </c>
+      <c r="G882" t="s">
+        <v>65</v>
+      </c>
+      <c r="J882" t="s">
+        <v>59</v>
+      </c>
+      <c r="L882" t="s">
+        <v>45</v>
+      </c>
+      <c r="N882" s="1">
+        <v>4</v>
+      </c>
+      <c r="O882" s="1">
+        <v>7</v>
+      </c>
+      <c r="P882" t="s">
+        <v>35</v>
+      </c>
+      <c r="R882">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="883" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A883" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B883" s="2">
+        <v>45117</v>
+      </c>
+      <c r="C883" t="s">
+        <v>114</v>
+      </c>
+      <c r="D883">
+        <v>1</v>
+      </c>
+      <c r="E883" t="s">
+        <v>59</v>
+      </c>
+      <c r="F883" t="s">
+        <v>1589</v>
+      </c>
+      <c r="G883" t="s">
+        <v>29</v>
+      </c>
+      <c r="H883" t="s">
+        <v>30</v>
+      </c>
+      <c r="J883" t="s">
+        <v>59</v>
+      </c>
+      <c r="L883" t="s">
+        <v>32</v>
+      </c>
+      <c r="N883" s="1">
+        <v>6</v>
+      </c>
+      <c r="O883" s="1">
+        <v>25</v>
+      </c>
+      <c r="P883" t="s">
+        <v>89</v>
+      </c>
+      <c r="R883">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="884" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A884" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B884" s="2">
+        <v>45120</v>
+      </c>
+      <c r="C884" t="s">
+        <v>114</v>
+      </c>
+      <c r="D884">
+        <v>1</v>
+      </c>
+      <c r="E884" t="s">
+        <v>59</v>
+      </c>
+      <c r="F884" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G884" t="s">
+        <v>29</v>
+      </c>
+      <c r="H884" t="s">
+        <v>30</v>
+      </c>
+      <c r="J884" t="s">
+        <v>59</v>
+      </c>
+      <c r="L884" t="s">
+        <v>32</v>
+      </c>
+      <c r="N884" s="1">
+        <v>5</v>
+      </c>
+      <c r="O884" s="1">
+        <v>11</v>
+      </c>
+      <c r="P884" t="s">
+        <v>89</v>
+      </c>
+      <c r="R884">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="885" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A885" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B885" s="2">
+        <v>45124</v>
+      </c>
+      <c r="C885" t="s">
+        <v>114</v>
+      </c>
+      <c r="D885">
+        <v>1</v>
+      </c>
+      <c r="E885" t="s">
+        <v>59</v>
+      </c>
+      <c r="F885" t="s">
+        <v>1593</v>
+      </c>
+      <c r="G885" t="s">
+        <v>65</v>
+      </c>
+      <c r="J885" t="s">
+        <v>59</v>
+      </c>
+      <c r="L885" t="s">
+        <v>45</v>
+      </c>
+      <c r="N885" s="1">
+        <v>3</v>
+      </c>
+      <c r="O885" s="1">
+        <v>9</v>
+      </c>
+      <c r="P885" t="s">
+        <v>35</v>
+      </c>
+      <c r="R885">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="886" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A886" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B886" s="2">
+        <v>45126</v>
+      </c>
+      <c r="C886" t="s">
+        <v>114</v>
+      </c>
+      <c r="D886">
+        <v>1</v>
+      </c>
+      <c r="E886" t="s">
+        <v>59</v>
+      </c>
+      <c r="F886" t="s">
+        <v>1595</v>
+      </c>
+      <c r="G886" t="s">
+        <v>29</v>
+      </c>
+      <c r="H886" t="s">
+        <v>30</v>
+      </c>
+      <c r="J886" t="s">
+        <v>249</v>
+      </c>
+      <c r="L886" t="s">
+        <v>32</v>
+      </c>
+      <c r="N886" s="1">
+        <v>6</v>
+      </c>
+      <c r="O886" s="1">
+        <v>18</v>
+      </c>
+      <c r="P886" t="s">
+        <v>89</v>
+      </c>
+      <c r="R886">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="887" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A887" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B887" s="2">
+        <v>45099</v>
+      </c>
+      <c r="C887" t="s">
+        <v>114</v>
+      </c>
+      <c r="D887">
+        <v>1</v>
+      </c>
+      <c r="E887" t="s">
+        <v>37</v>
+      </c>
+      <c r="F887" t="s">
+        <v>435</v>
+      </c>
+      <c r="G887" t="s">
+        <v>29</v>
+      </c>
+      <c r="J887" t="s">
+        <v>37</v>
+      </c>
+      <c r="L887" t="s">
+        <v>32</v>
+      </c>
+      <c r="N887" s="1">
+        <v>6</v>
+      </c>
+      <c r="O887" s="1">
+        <v>10</v>
+      </c>
+      <c r="R887">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="888" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A888" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B888" s="2">
+        <v>45099</v>
+      </c>
+      <c r="C888" t="s">
+        <v>114</v>
+      </c>
+      <c r="D888">
+        <v>1</v>
+      </c>
+      <c r="E888" t="s">
+        <v>37</v>
+      </c>
+      <c r="F888" t="s">
+        <v>1598</v>
+      </c>
+      <c r="G888" t="s">
+        <v>29</v>
+      </c>
+      <c r="J888" t="s">
+        <v>54</v>
+      </c>
+      <c r="K888" t="s">
+        <v>415</v>
+      </c>
+      <c r="L888" t="s">
+        <v>32</v>
+      </c>
+      <c r="N888" s="1">
+        <v>5</v>
+      </c>
+      <c r="O888" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="889" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A889" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B889" s="2">
+        <v>45099</v>
+      </c>
+      <c r="C889" t="s">
+        <v>114</v>
+      </c>
+      <c r="D889">
+        <v>1</v>
+      </c>
+      <c r="E889" t="s">
+        <v>37</v>
+      </c>
+      <c r="F889" t="s">
+        <v>1600</v>
+      </c>
+      <c r="G889" t="s">
+        <v>29</v>
+      </c>
+      <c r="J889" t="s">
+        <v>54</v>
+      </c>
+      <c r="L889" t="s">
+        <v>32</v>
+      </c>
+      <c r="N889" s="1">
+        <v>9</v>
+      </c>
+      <c r="O889" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="890" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A890" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B890" s="2">
+        <v>45099</v>
+      </c>
+      <c r="C890" t="s">
+        <v>114</v>
+      </c>
+      <c r="D890">
+        <v>1</v>
+      </c>
+      <c r="E890" t="s">
+        <v>37</v>
+      </c>
+      <c r="F890" t="s">
+        <v>1602</v>
+      </c>
+      <c r="G890" t="s">
+        <v>29</v>
+      </c>
+      <c r="J890" t="s">
+        <v>37</v>
+      </c>
+      <c r="L890" t="s">
+        <v>32</v>
+      </c>
+      <c r="N890" s="1">
+        <v>7</v>
+      </c>
+      <c r="O890" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="891" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A891" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B891" s="2">
+        <v>45099</v>
+      </c>
+      <c r="C891" t="s">
+        <v>114</v>
+      </c>
+      <c r="D891">
+        <v>1</v>
+      </c>
+      <c r="E891" t="s">
+        <v>37</v>
+      </c>
+      <c r="F891" t="s">
+        <v>1553</v>
+      </c>
+      <c r="G891" t="s">
+        <v>29</v>
+      </c>
+      <c r="J891" t="s">
+        <v>54</v>
+      </c>
+      <c r="L891" t="s">
+        <v>32</v>
+      </c>
+      <c r="N891" s="1">
+        <v>8</v>
+      </c>
+      <c r="O891" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="892" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A892" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B892" s="2">
+        <v>45099</v>
+      </c>
+      <c r="C892" t="s">
+        <v>114</v>
+      </c>
+      <c r="D892">
+        <v>1</v>
+      </c>
+      <c r="E892" t="s">
+        <v>37</v>
+      </c>
+      <c r="F892" t="s">
+        <v>1605</v>
+      </c>
+      <c r="G892" t="s">
+        <v>29</v>
+      </c>
+      <c r="J892" t="s">
+        <v>37</v>
+      </c>
+      <c r="L892" t="s">
+        <v>32</v>
+      </c>
+      <c r="N892" s="1">
+        <v>9</v>
+      </c>
+      <c r="O892" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="893" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A893" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B893" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C893" t="s">
+        <v>114</v>
+      </c>
+      <c r="D893">
+        <v>1</v>
+      </c>
+      <c r="E893" t="s">
+        <v>37</v>
+      </c>
+      <c r="F893" t="s">
+        <v>508</v>
+      </c>
+      <c r="G893" t="s">
+        <v>29</v>
+      </c>
+      <c r="J893" t="s">
+        <v>37</v>
+      </c>
+      <c r="L893" t="s">
+        <v>32</v>
+      </c>
+      <c r="N893" s="1">
+        <v>5</v>
+      </c>
+      <c r="O893" s="1">
+        <v>10</v>
+      </c>
+      <c r="R893">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="894" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A894" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B894" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C894" t="s">
+        <v>114</v>
+      </c>
+      <c r="D894">
+        <v>1</v>
+      </c>
+      <c r="E894" t="s">
+        <v>37</v>
+      </c>
+      <c r="F894" t="s">
+        <v>541</v>
+      </c>
+      <c r="G894" t="s">
+        <v>29</v>
+      </c>
+      <c r="J894" t="s">
+        <v>54</v>
+      </c>
+      <c r="L894" t="s">
+        <v>32</v>
+      </c>
+      <c r="N894" s="1">
+        <v>9</v>
+      </c>
+      <c r="O894" s="1">
+        <v>16</v>
+      </c>
+      <c r="R894">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="895" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A895" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B895" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C895" t="s">
+        <v>114</v>
+      </c>
+      <c r="D895">
+        <v>1</v>
+      </c>
+      <c r="E895" t="s">
+        <v>37</v>
+      </c>
+      <c r="F895" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G895" t="s">
+        <v>29</v>
+      </c>
+      <c r="J895" t="s">
+        <v>37</v>
+      </c>
+      <c r="L895" t="s">
+        <v>32</v>
+      </c>
+      <c r="N895" s="1">
+        <v>4</v>
+      </c>
+      <c r="O895" s="1">
+        <v>8</v>
+      </c>
+      <c r="R895">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="896" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A896" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B896" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C896" t="s">
+        <v>114</v>
+      </c>
+      <c r="D896">
+        <v>1</v>
+      </c>
+      <c r="E896" t="s">
+        <v>37</v>
+      </c>
+      <c r="F896" t="s">
+        <v>1611</v>
+      </c>
+      <c r="G896" t="s">
+        <v>29</v>
+      </c>
+      <c r="J896" t="s">
+        <v>37</v>
+      </c>
+      <c r="L896" t="s">
+        <v>32</v>
+      </c>
+      <c r="N896" s="1">
+        <v>9</v>
+      </c>
+      <c r="O896" s="1">
+        <v>11</v>
+      </c>
+      <c r="R896">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="897" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A897" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B897" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C897" t="s">
+        <v>114</v>
+      </c>
+      <c r="D897">
+        <v>1</v>
+      </c>
+      <c r="E897" t="s">
+        <v>37</v>
+      </c>
+      <c r="F897" t="s">
+        <v>1613</v>
+      </c>
+      <c r="G897" t="s">
+        <v>29</v>
+      </c>
+      <c r="J897" t="s">
+        <v>37</v>
+      </c>
+      <c r="L897" t="s">
+        <v>32</v>
+      </c>
+      <c r="N897" s="1">
+        <v>4</v>
+      </c>
+      <c r="O897" s="1">
+        <v>7</v>
+      </c>
+      <c r="R897">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="898" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A898" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B898" s="2">
+        <v>44930</v>
+      </c>
+      <c r="C898" t="s">
+        <v>114</v>
+      </c>
+      <c r="D898">
+        <v>1</v>
+      </c>
+      <c r="E898" t="s">
+        <v>37</v>
+      </c>
+      <c r="F898" t="s">
+        <v>28</v>
+      </c>
+      <c r="G898" t="s">
+        <v>29</v>
+      </c>
+      <c r="J898" t="s">
+        <v>31</v>
+      </c>
+      <c r="L898" t="s">
+        <v>32</v>
+      </c>
+      <c r="N898" s="1">
+        <v>5</v>
+      </c>
+      <c r="O898" s="1">
+        <v>16</v>
+      </c>
+      <c r="P898" t="s">
+        <v>89</v>
+      </c>
+      <c r="R898">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="899" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A899" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B899" s="2">
+        <v>44932</v>
+      </c>
+      <c r="C899" t="s">
+        <v>114</v>
+      </c>
+      <c r="D899">
+        <v>1</v>
+      </c>
+      <c r="E899" t="s">
+        <v>37</v>
+      </c>
+      <c r="F899" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G899" t="s">
+        <v>29</v>
+      </c>
+      <c r="J899" t="s">
+        <v>54</v>
+      </c>
+      <c r="L899" t="s">
+        <v>32</v>
+      </c>
+      <c r="N899" s="1">
+        <v>5</v>
+      </c>
+      <c r="O899" s="1">
+        <v>6</v>
+      </c>
+      <c r="P899" t="s">
+        <v>89</v>
+      </c>
+      <c r="R899">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="900" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A900" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B900" s="2">
+        <v>44932</v>
+      </c>
+      <c r="C900" t="s">
+        <v>114</v>
+      </c>
+      <c r="D900">
+        <v>1</v>
+      </c>
+      <c r="E900" t="s">
+        <v>37</v>
+      </c>
+      <c r="F900" t="s">
+        <v>28</v>
+      </c>
+      <c r="G900" t="s">
+        <v>29</v>
+      </c>
+      <c r="J900" t="s">
+        <v>350</v>
+      </c>
+      <c r="L900" t="s">
+        <v>32</v>
+      </c>
+      <c r="N900" s="1">
+        <v>5</v>
+      </c>
+      <c r="O900" s="1">
+        <v>13</v>
+      </c>
+      <c r="P900" t="s">
+        <v>89</v>
+      </c>
+      <c r="R900">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="901" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A901" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B901" s="2">
+        <v>44936</v>
+      </c>
+      <c r="C901" t="s">
+        <v>114</v>
+      </c>
+      <c r="D901">
+        <v>1</v>
+      </c>
+      <c r="E901" t="s">
+        <v>37</v>
+      </c>
+      <c r="F901" t="s">
+        <v>28</v>
+      </c>
+      <c r="G901" t="s">
+        <v>29</v>
+      </c>
+      <c r="J901" t="s">
+        <v>683</v>
+      </c>
+      <c r="L901" t="s">
+        <v>32</v>
+      </c>
+      <c r="N901" s="1">
+        <v>5</v>
+      </c>
+      <c r="O901" s="1">
+        <v>16</v>
+      </c>
+      <c r="P901" t="s">
+        <v>89</v>
+      </c>
+      <c r="R901">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="902" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A902" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B902" s="2">
+        <v>44936</v>
+      </c>
+      <c r="C902" t="s">
+        <v>114</v>
+      </c>
+      <c r="D902">
+        <v>1</v>
+      </c>
+      <c r="E902" t="s">
+        <v>37</v>
+      </c>
+      <c r="F902" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G902" t="s">
+        <v>29</v>
+      </c>
+      <c r="J902" t="s">
+        <v>350</v>
+      </c>
+      <c r="L902" t="s">
+        <v>32</v>
+      </c>
+      <c r="N902" s="1">
+        <v>6</v>
+      </c>
+      <c r="O902" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="P902" t="s">
+        <v>89</v>
+      </c>
+      <c r="R902">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="903" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A903" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B903" s="2">
+        <v>44946</v>
+      </c>
+      <c r="C903" t="s">
+        <v>114</v>
+      </c>
+      <c r="D903">
+        <v>1</v>
+      </c>
+      <c r="E903" t="s">
+        <v>37</v>
+      </c>
+      <c r="F903" t="s">
+        <v>28</v>
+      </c>
+      <c r="G903" t="s">
+        <v>29</v>
+      </c>
+      <c r="J903" t="s">
+        <v>302</v>
+      </c>
+      <c r="L903" t="s">
+        <v>32</v>
+      </c>
+      <c r="N903" s="1">
+        <v>5</v>
+      </c>
+      <c r="O903" s="1">
+        <v>10</v>
+      </c>
+      <c r="P903" t="s">
+        <v>89</v>
+      </c>
+      <c r="R903">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="904" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A904" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B904" s="2">
+        <v>44946</v>
+      </c>
+      <c r="C904" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D904" s="6">
+        <v>1</v>
+      </c>
+      <c r="E904" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F904" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G904" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J904" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L904" t="s">
+        <v>32</v>
+      </c>
+      <c r="N904" s="1">
+        <v>5</v>
+      </c>
+      <c r="O904" s="1">
+        <v>9</v>
+      </c>
+      <c r="P904" t="s">
+        <v>89</v>
+      </c>
+      <c r="R904">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="905" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A905" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B905" s="2">
+        <v>44949</v>
+      </c>
+      <c r="C905" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D905" s="6">
+        <v>1</v>
+      </c>
+      <c r="E905" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F905" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G905" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J905" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="L905" t="s">
+        <v>32</v>
+      </c>
+      <c r="N905" s="1">
+        <v>5</v>
+      </c>
+      <c r="O905" s="1">
+        <v>15.5</v>
+      </c>
+      <c r="P905" t="s">
+        <v>89</v>
+      </c>
+      <c r="R905">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="906" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A906" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B906" s="2">
+        <v>44949</v>
+      </c>
+      <c r="C906" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D906" s="6">
+        <v>1</v>
+      </c>
+      <c r="E906" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F906" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G906" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J906" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="L906" t="s">
+        <v>32</v>
+      </c>
+      <c r="N906" s="1">
+        <v>5</v>
+      </c>
+      <c r="O906" s="1">
+        <v>6</v>
+      </c>
+      <c r="P906" t="s">
+        <v>89</v>
+      </c>
+      <c r="R906">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="907" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A907" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B907" s="9">
+        <v>44949</v>
+      </c>
+      <c r="C907" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D907" s="6">
+        <v>1</v>
+      </c>
+      <c r="E907" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F907" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G907" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J907" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="L907" t="s">
+        <v>32</v>
+      </c>
+      <c r="N907" s="1">
+        <v>5</v>
+      </c>
+      <c r="O907" s="1">
+        <v>10</v>
+      </c>
+      <c r="P907" t="s">
+        <v>89</v>
+      </c>
+      <c r="R907">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="908" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A908" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B908" s="2">
+        <v>44950</v>
+      </c>
+      <c r="C908" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D908" s="6">
+        <v>1</v>
+      </c>
+      <c r="E908" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F908" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G908" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J908" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L908" t="s">
+        <v>32</v>
+      </c>
+      <c r="N908" s="1">
+        <v>6</v>
+      </c>
+      <c r="O908" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="P908" t="s">
+        <v>89</v>
+      </c>
+      <c r="R908">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="909" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A909" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B909" s="2">
+        <v>44950</v>
+      </c>
+      <c r="C909" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D909" s="6">
+        <v>1</v>
+      </c>
+      <c r="E909" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F909" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G909" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J909" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="L909" t="s">
+        <v>32</v>
+      </c>
+      <c r="N909" s="1">
+        <v>6</v>
+      </c>
+      <c r="O909" s="1">
+        <v>13</v>
+      </c>
+      <c r="P909" t="s">
+        <v>89</v>
+      </c>
+      <c r="R909">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="910" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A910" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B910" s="9">
+        <v>44950</v>
+      </c>
+      <c r="C910" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D910" s="6">
+        <v>1</v>
+      </c>
+      <c r="E910" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F910" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G910" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J910" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L910" t="s">
+        <v>32</v>
+      </c>
+      <c r="N910" s="1">
+        <v>6</v>
+      </c>
+      <c r="O910" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="P910" t="s">
+        <v>89</v>
+      </c>
+      <c r="R910">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="911" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A911" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B911" s="2">
+        <v>44953</v>
+      </c>
+      <c r="C911" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D911" s="6">
+        <v>1</v>
+      </c>
+      <c r="E911" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F911" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G911" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J911" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L911" t="s">
+        <v>32</v>
+      </c>
+      <c r="N911" s="1">
+        <v>6</v>
+      </c>
+      <c r="O911" s="1">
+        <v>14</v>
+      </c>
+      <c r="P911" t="s">
+        <v>89</v>
+      </c>
+      <c r="R911">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="912" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A912" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B912" s="2">
+        <v>44953</v>
+      </c>
+      <c r="C912" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D912" s="6">
+        <v>1</v>
+      </c>
+      <c r="E912" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F912" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G912" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J912" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L912" t="s">
+        <v>32</v>
+      </c>
+      <c r="N912" s="1">
+        <v>6</v>
+      </c>
+      <c r="O912" s="1">
+        <v>11</v>
+      </c>
+      <c r="P912" t="s">
+        <v>89</v>
+      </c>
+      <c r="R912">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="913" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A913" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B913" s="2">
+        <v>44957</v>
+      </c>
+      <c r="C913" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D913" s="6">
+        <v>1</v>
+      </c>
+      <c r="E913" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F913" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G913" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J913" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="L913" t="s">
+        <v>32</v>
+      </c>
+      <c r="N913" s="1">
+        <v>6</v>
+      </c>
+      <c r="O913" s="1">
+        <v>17</v>
+      </c>
+      <c r="P913" t="s">
+        <v>89</v>
+      </c>
+      <c r="R913">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="914" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A914" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B914" s="2">
+        <v>44957</v>
+      </c>
+      <c r="C914" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D914" s="6">
+        <v>1</v>
+      </c>
+      <c r="E914" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F914" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G914" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J914" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K914" t="s">
+        <v>722</v>
+      </c>
+      <c r="L914" t="s">
+        <v>32</v>
+      </c>
+      <c r="N914" s="1">
+        <v>6</v>
+      </c>
+      <c r="O914" s="1">
+        <v>7</v>
+      </c>
+      <c r="P914" t="s">
+        <v>89</v>
+      </c>
+      <c r="R914">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="915" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A915" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B915" s="2">
+        <v>45121</v>
+      </c>
+      <c r="C915" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D915" s="6">
+        <v>1</v>
+      </c>
+      <c r="E915" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F915" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="G915" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J915" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K915" t="s">
+        <v>336</v>
+      </c>
+      <c r="N915" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O915" s="1">
+        <v>3</v>
+      </c>
+      <c r="P915" t="s">
+        <v>35</v>
+      </c>
+      <c r="R915">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="916" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A916" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B916" s="2">
+        <v>45121</v>
+      </c>
+      <c r="C916" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D916" s="6">
+        <v>1</v>
+      </c>
+      <c r="E916" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F916" s="6" t="s">
+        <v>1679</v>
+      </c>
+      <c r="G916" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="H916" s="6"/>
+      <c r="J916" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K916" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="L916" t="s">
+        <v>32</v>
+      </c>
+      <c r="N916" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O916" s="1">
+        <v>4</v>
+      </c>
+      <c r="P916" t="s">
+        <v>35</v>
+      </c>
+      <c r="R916">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="917" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A917" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B917" s="2">
+        <v>45121</v>
+      </c>
+      <c r="C917" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D917" s="6">
+        <v>1</v>
+      </c>
+      <c r="E917" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F917" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G917" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J917" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="L917" t="s">
+        <v>32</v>
+      </c>
+      <c r="N917" s="1">
+        <v>5</v>
+      </c>
+      <c r="O917" s="1">
+        <v>10</v>
+      </c>
+      <c r="P917" t="s">
+        <v>89</v>
+      </c>
+      <c r="R917">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="918" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A918" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B918" s="2">
+        <v>45123</v>
+      </c>
+      <c r="C918" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D918" s="6">
+        <v>1</v>
+      </c>
+      <c r="E918" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F918" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G918" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J918" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K918" s="6" t="s">
+        <v>1273</v>
+      </c>
+      <c r="L918" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N918" s="1">
+        <v>3</v>
+      </c>
+      <c r="O918" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="P918" t="s">
+        <v>89</v>
+      </c>
+      <c r="R918">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="919" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A919" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B919" s="2">
+        <v>45123</v>
+      </c>
+      <c r="C919" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D919" s="6">
+        <v>1</v>
+      </c>
+      <c r="E919" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F919" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G919" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J919" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L919" t="s">
+        <v>32</v>
+      </c>
+      <c r="N919" s="1">
+        <v>5</v>
+      </c>
+      <c r="O919" s="1">
+        <v>5</v>
+      </c>
+      <c r="P919" t="s">
+        <v>89</v>
+      </c>
+      <c r="R919">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="920" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A920" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B920" s="2">
+        <v>45124</v>
+      </c>
+      <c r="C920" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D920" s="6">
+        <v>1</v>
+      </c>
+      <c r="E920" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F920" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G920" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J920" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="L920" t="s">
+        <v>32</v>
+      </c>
+      <c r="N920" s="1">
+        <v>7</v>
+      </c>
+      <c r="O920" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="P920" t="s">
+        <v>89</v>
+      </c>
+      <c r="R920">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="921" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A921" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B921" s="2">
+        <v>45124</v>
+      </c>
+      <c r="C921" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D921" s="6">
+        <v>1</v>
+      </c>
+      <c r="E921" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F921" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G921" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J921" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="L921" t="s">
+        <v>32</v>
+      </c>
+      <c r="N921" s="1">
+        <v>6</v>
+      </c>
+      <c r="O921" s="1">
+        <v>6</v>
+      </c>
+      <c r="P921" t="s">
+        <v>89</v>
+      </c>
+      <c r="R921">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="922" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A922" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B922" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C922" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D922" s="6">
+        <v>1</v>
+      </c>
+      <c r="E922" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F922" t="s">
+        <v>454</v>
+      </c>
+      <c r="G922" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J922" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K922" t="s">
+        <v>320</v>
+      </c>
+      <c r="L922" t="s">
+        <v>32</v>
+      </c>
+      <c r="N922" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="O922" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="P922" t="s">
+        <v>89</v>
+      </c>
+      <c r="R922">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="923" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A923" t="s">
+        <v>1639</v>
+      </c>
+      <c r="B923" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C923" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D923" s="6">
+        <v>1</v>
+      </c>
+      <c r="E923" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F923" s="6" t="s">
+        <v>1553</v>
+      </c>
+      <c r="G923" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J923" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="L923" t="s">
+        <v>32</v>
+      </c>
+      <c r="N923" s="1">
+        <v>6</v>
+      </c>
+      <c r="O923" s="1">
+        <v>6</v>
+      </c>
+      <c r="P923" t="s">
+        <v>89</v>
+      </c>
+      <c r="R923">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="924" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A924" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B924" s="9">
+        <v>45127</v>
+      </c>
+      <c r="C924" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D924" s="6">
+        <v>1</v>
+      </c>
+      <c r="E924" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F924" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="G924" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J924" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="L924" t="s">
+        <v>32</v>
+      </c>
+      <c r="N924" s="1">
+        <v>4</v>
+      </c>
+      <c r="O924" s="1">
+        <v>3</v>
+      </c>
+      <c r="P924" t="s">
+        <v>89</v>
+      </c>
+      <c r="R924">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="925" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A925" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B925" s="2">
+        <v>45135</v>
+      </c>
+      <c r="C925" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D925" s="6">
+        <v>1</v>
+      </c>
+      <c r="E925" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F925" s="6" t="s">
+        <v>1611</v>
+      </c>
+      <c r="G925" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J925" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L925" t="s">
+        <v>32</v>
+      </c>
+      <c r="N925" s="1">
+        <v>5</v>
+      </c>
+      <c r="O925" s="1">
+        <v>4</v>
+      </c>
+      <c r="P925" t="s">
+        <v>89</v>
+      </c>
+      <c r="R925">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="926" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A926" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B926" s="2">
+        <v>45135</v>
+      </c>
+      <c r="C926" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D926" s="6">
+        <v>1</v>
+      </c>
+      <c r="E926" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F926" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="G926" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J926" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L926" t="s">
+        <v>32</v>
+      </c>
+      <c r="N926" s="1">
+        <v>4</v>
+      </c>
+      <c r="O926" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="P926" t="s">
+        <v>89</v>
+      </c>
+      <c r="R926">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="927" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A927" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B927" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C927" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D927" s="6">
+        <v>1</v>
+      </c>
+      <c r="E927" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F927" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G927" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J927" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="L927" t="s">
+        <v>32</v>
+      </c>
+      <c r="N927" s="1">
+        <v>6</v>
+      </c>
+      <c r="O927" s="1">
+        <v>12</v>
+      </c>
+      <c r="P927" t="s">
+        <v>89</v>
+      </c>
+      <c r="R927">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="928" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A928" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B928" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C928" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D928" s="6">
+        <v>1</v>
+      </c>
+      <c r="E928" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F928" s="6" t="s">
+        <v>1553</v>
+      </c>
+      <c r="G928" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J928" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="L928" t="s">
+        <v>32</v>
+      </c>
+      <c r="N928" s="1">
+        <v>4</v>
+      </c>
+      <c r="O928" s="1">
+        <v>5</v>
+      </c>
+      <c r="P928" t="s">
+        <v>89</v>
+      </c>
+      <c r="R928">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="929" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A929" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B929" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C929" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D929" s="6">
+        <v>1</v>
+      </c>
+      <c r="E929" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F929" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="G929" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="J929" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K929" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="L929" t="s">
+        <v>32</v>
+      </c>
+      <c r="N929" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="O929" s="1">
+        <v>11</v>
+      </c>
+      <c r="P929" t="s">
+        <v>89</v>
+      </c>
+      <c r="R929">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="930" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A930" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B930" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C930" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D930" s="6">
+        <v>1</v>
+      </c>
+      <c r="E930" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F930" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="G930" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="J930" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K930" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="L930" t="s">
+        <v>32</v>
+      </c>
+      <c r="N930" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="O930" s="1">
+        <v>16</v>
+      </c>
+      <c r="P930" t="s">
+        <v>89</v>
+      </c>
+      <c r="R930">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="931" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A931" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B931" s="2">
+        <v>45148</v>
+      </c>
+      <c r="C931" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D931" s="6">
+        <v>1</v>
+      </c>
+      <c r="E931" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F931" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="G931" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="J931" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K931" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="L931" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N931" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="O931" s="1">
+        <v>8</v>
+      </c>
+      <c r="P931" t="s">
+        <v>89</v>
+      </c>
+      <c r="R931">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="932" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A932" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B932" s="2">
+        <v>45148</v>
+      </c>
+      <c r="C932" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D932" s="6">
+        <v>1</v>
+      </c>
+      <c r="E932" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F932" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="G932" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="J932" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K932" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="L932" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N932" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="O932" s="1">
+        <v>7</v>
+      </c>
+      <c r="P932" t="s">
+        <v>89</v>
+      </c>
+      <c r="R932">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="933" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A933" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B933" s="2">
+        <v>45148</v>
+      </c>
+      <c r="C933" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D933" s="6">
+        <v>1</v>
+      </c>
+      <c r="E933" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F933" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="G933" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J933" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L933" t="s">
+        <v>32</v>
+      </c>
+      <c r="N933" s="1">
+        <v>5</v>
+      </c>
+      <c r="O933" s="1">
+        <v>3</v>
+      </c>
+      <c r="P933" t="s">
+        <v>89</v>
+      </c>
+      <c r="R933">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="934" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A934" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B934" s="2">
+        <v>45153</v>
+      </c>
+      <c r="C934" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D934" s="6">
+        <v>1</v>
+      </c>
+      <c r="E934" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F934" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G934" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J934" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L934" t="s">
+        <v>32</v>
+      </c>
+      <c r="N934" s="1">
+        <v>6</v>
+      </c>
+      <c r="O934" s="1">
+        <v>12</v>
+      </c>
+      <c r="P934" t="s">
+        <v>89</v>
+      </c>
+      <c r="R934">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="935" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A935" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B935" s="2">
+        <v>45153</v>
+      </c>
+      <c r="C935" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D935" s="6">
+        <v>1</v>
+      </c>
+      <c r="E935" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F935" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="G935" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J935" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="N935" s="1">
+        <v>4</v>
+      </c>
+      <c r="O935" s="1">
+        <v>13</v>
+      </c>
+      <c r="P935" t="s">
+        <v>89</v>
+      </c>
+      <c r="R935">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="936" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A936" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B936" s="2">
+        <v>45156</v>
+      </c>
+      <c r="C936" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D936" s="6">
+        <v>1</v>
+      </c>
+      <c r="E936" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F936" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="G936" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J936" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="N936" s="1">
+        <v>5</v>
+      </c>
+      <c r="O936" s="1">
+        <v>8</v>
+      </c>
+      <c r="P936" t="s">
+        <v>89</v>
+      </c>
+      <c r="R936">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="937" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A937" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B937" s="9">
+        <v>45156</v>
+      </c>
+      <c r="C937" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D937" s="6">
+        <v>1</v>
+      </c>
+      <c r="E937" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F937" s="6" t="s">
+        <v>1680</v>
+      </c>
+      <c r="G937" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J937" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="N937" s="1">
+        <v>4</v>
+      </c>
+      <c r="O937" s="1">
+        <v>3</v>
+      </c>
+      <c r="P937" t="s">
+        <v>89</v>
+      </c>
+      <c r="R937">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="938" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A938" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B938" s="9">
+        <v>45156</v>
+      </c>
+      <c r="C938" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D938" s="6">
+        <v>1</v>
+      </c>
+      <c r="E938" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F938" s="6" t="s">
+        <v>1681</v>
+      </c>
+      <c r="G938" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J938" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K938" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="N938" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="O938" s="1">
+        <v>6</v>
+      </c>
+      <c r="P938" t="s">
+        <v>89</v>
+      </c>
+      <c r="R938">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="939" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A939" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B939" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C939" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D939" s="6">
+        <v>1</v>
+      </c>
+      <c r="E939" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F939" s="6" t="s">
+        <v>1682</v>
+      </c>
+      <c r="G939" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H939" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="J939" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L939" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N939" s="1">
+        <v>3</v>
+      </c>
+      <c r="O939" s="1">
+        <v>5</v>
+      </c>
+      <c r="P939" t="s">
+        <v>89</v>
+      </c>
+      <c r="R939">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="940" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A940" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B940" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C940" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D940" s="6">
+        <v>1</v>
+      </c>
+      <c r="E940" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F940" s="6" t="s">
+        <v>1683</v>
+      </c>
+      <c r="G940" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="J940" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L940" t="s">
+        <v>45</v>
+      </c>
+      <c r="N940" s="1">
+        <v>1</v>
+      </c>
+      <c r="O940" s="1">
+        <v>6</v>
+      </c>
+      <c r="P940" t="s">
+        <v>89</v>
+      </c>
+      <c r="R940">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="941" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A941" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B941" s="2">
+        <v>45135</v>
+      </c>
+      <c r="C941" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D941" s="6">
+        <v>1</v>
+      </c>
+      <c r="E941" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F941" s="6" t="s">
+        <v>1684</v>
+      </c>
+      <c r="G941" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H941" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="K941" s="6" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L941" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N941" s="1">
+        <v>2</v>
+      </c>
+      <c r="O941" s="1">
+        <v>4</v>
+      </c>
+      <c r="P941" t="s">
+        <v>89</v>
+      </c>
+      <c r="R941">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="942" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A942" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B942" s="2">
+        <v>45136</v>
+      </c>
+      <c r="C942" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D942" s="6">
+        <v>1</v>
+      </c>
+      <c r="E942" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F942" s="6" t="s">
+        <v>1686</v>
+      </c>
+      <c r="G942" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J942" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L942" t="s">
+        <v>45</v>
+      </c>
+      <c r="N942" s="1">
+        <v>2</v>
+      </c>
+      <c r="O942" s="1">
+        <v>2</v>
+      </c>
+      <c r="P942" t="s">
+        <v>82</v>
+      </c>
+      <c r="S942" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="943" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A943" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B943" s="2">
+        <v>45139</v>
+      </c>
+      <c r="C943" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D943" s="6">
+        <v>1</v>
+      </c>
+      <c r="E943" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F943" s="6" t="s">
+        <v>1682</v>
+      </c>
+      <c r="G943" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K943" t="s">
+        <v>1687</v>
+      </c>
+      <c r="L943" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N943" s="1">
+        <v>2</v>
+      </c>
+      <c r="O943" s="1">
+        <v>6</v>
+      </c>
+      <c r="P943" t="s">
+        <v>35</v>
+      </c>
+      <c r="R943">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="944" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A944" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B944" s="2">
+        <v>45139</v>
+      </c>
+      <c r="C944" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D944" s="6">
+        <v>1</v>
+      </c>
+      <c r="E944" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F944" s="6" t="s">
+        <v>1688</v>
+      </c>
+      <c r="G944" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J944" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L944" t="s">
+        <v>32</v>
+      </c>
+      <c r="N944" s="1">
+        <v>2</v>
+      </c>
+      <c r="O944" s="1">
+        <v>8</v>
+      </c>
+      <c r="P944" t="s">
+        <v>35</v>
+      </c>
+      <c r="R944">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="945" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A945" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B945" s="2">
+        <v>45157</v>
+      </c>
+      <c r="C945" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D945" s="6">
+        <v>1</v>
+      </c>
+      <c r="E945" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F945" s="6" t="s">
+        <v>1689</v>
+      </c>
+      <c r="G945" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="J945" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L945" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N945" s="1">
+        <v>5</v>
+      </c>
+      <c r="O945" s="1">
+        <v>5</v>
+      </c>
+      <c r="P945" t="s">
+        <v>89</v>
+      </c>
+      <c r="R945">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="946" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A946" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B946" s="2">
+        <v>45161</v>
+      </c>
+      <c r="C946" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D946" s="6">
+        <v>1</v>
+      </c>
+      <c r="E946" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F946" s="6" t="s">
+        <v>1689</v>
+      </c>
+      <c r="G946" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="J946" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L946" t="s">
+        <v>32</v>
+      </c>
+      <c r="N946" s="1">
+        <v>2</v>
+      </c>
+      <c r="O946" s="1">
+        <v>6</v>
+      </c>
+      <c r="P946" t="s">
+        <v>35</v>
+      </c>
+      <c r="R946">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="947" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A947" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B947" s="2">
+        <v>45165</v>
+      </c>
+      <c r="C947" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D947" s="6">
+        <v>1</v>
+      </c>
+      <c r="E947" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F947" s="6" t="s">
+        <v>1690</v>
+      </c>
+      <c r="G947" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H947" s="6" t="s">
+        <v>1557</v>
+      </c>
+      <c r="J947" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K947" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="L947" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N947" s="1">
+        <v>2</v>
+      </c>
+      <c r="O947" s="1">
+        <v>4</v>
+      </c>
+      <c r="P947" t="s">
+        <v>35</v>
+      </c>
+      <c r="R947">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="948" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A948" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B948" s="2">
+        <v>45166</v>
+      </c>
+      <c r="C948" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D948" s="6">
+        <v>1</v>
+      </c>
+      <c r="E948" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F948" s="6" t="s">
+        <v>1691</v>
+      </c>
+      <c r="G948" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J948" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K948" s="6" t="s">
+        <v>1692</v>
+      </c>
+      <c r="L948" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N948" s="1">
+        <v>2</v>
+      </c>
+      <c r="O948" s="1">
+        <v>4</v>
+      </c>
+      <c r="P948" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="949" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A949" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B949" s="2">
+        <v>45166</v>
+      </c>
+      <c r="C949" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D949" s="6">
+        <v>1</v>
+      </c>
+      <c r="E949" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F949" s="6" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G949" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="J949" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="N949" s="1">
+        <v>2</v>
+      </c>
+      <c r="O949" s="1">
+        <v>10</v>
+      </c>
+      <c r="P949" t="s">
+        <v>35</v>
+      </c>
+      <c r="R949">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="950" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A950" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B950" s="2">
+        <v>45167</v>
+      </c>
+      <c r="C950" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D950" s="6">
+        <v>1</v>
+      </c>
+      <c r="E950" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F950" s="6" t="s">
+        <v>1694</v>
+      </c>
+      <c r="G950" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J950" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L950" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N950" s="1">
+        <v>4</v>
+      </c>
+      <c r="O950" s="1">
+        <v>8</v>
+      </c>
+      <c r="P950" t="s">
+        <v>35</v>
+      </c>
+      <c r="R950">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="951" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A951" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B951" s="2">
+        <v>45167</v>
+      </c>
+      <c r="C951" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D951" s="6">
+        <v>1</v>
+      </c>
+      <c r="E951" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F951" s="6" t="s">
+        <v>1695</v>
+      </c>
+      <c r="G951" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H951" s="6" t="s">
+        <v>1557</v>
+      </c>
+      <c r="J951" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L951" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N951" s="1">
+        <v>1</v>
+      </c>
+      <c r="O951" s="1">
+        <v>2</v>
+      </c>
+      <c r="P951" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="952" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A952" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B952" s="2">
+        <v>45175</v>
+      </c>
+      <c r="C952" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D952" s="6">
+        <v>1</v>
+      </c>
+      <c r="E952" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F952" s="6" t="s">
+        <v>1682</v>
+      </c>
+      <c r="G952" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="J952" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K952" s="6" t="s">
+        <v>1696</v>
+      </c>
+      <c r="N952" s="1">
+        <v>1</v>
+      </c>
+      <c r="O952" s="1">
+        <v>2</v>
+      </c>
+      <c r="P952" t="s">
+        <v>89</v>
+      </c>
+      <c r="R952">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="953" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A953" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B953" s="2">
+        <v>45175</v>
+      </c>
+      <c r="C953" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D953" s="6">
+        <v>1</v>
+      </c>
+      <c r="E953" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F953" s="6" t="s">
+        <v>1772</v>
+      </c>
+      <c r="G953" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J953" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L953" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N953" s="1">
+        <v>3</v>
+      </c>
+      <c r="O953" s="1">
+        <v>5</v>
+      </c>
+      <c r="P953" t="s">
+        <v>89</v>
+      </c>
+      <c r="R953">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="954" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A954" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B954" s="2">
+        <v>45176</v>
+      </c>
+      <c r="C954" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D954" s="6">
+        <v>1</v>
+      </c>
+      <c r="E954" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F954" s="6" t="s">
+        <v>1772</v>
+      </c>
+      <c r="G954" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J954" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="L954" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N954" s="1">
+        <v>2</v>
+      </c>
+      <c r="O954" s="1">
+        <v>2</v>
+      </c>
+      <c r="P954" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="955" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A955" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B955" s="2">
+        <v>45176</v>
+      </c>
+      <c r="C955" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D955" s="6">
+        <v>1</v>
+      </c>
+      <c r="E955" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F955" s="6" t="s">
+        <v>1695</v>
+      </c>
+      <c r="G955" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J955" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L955" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N955" s="1">
+        <v>2</v>
+      </c>
+      <c r="O955" s="1">
+        <v>2</v>
+      </c>
+      <c r="P955" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="956" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A956" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B956" s="2">
+        <v>45183</v>
+      </c>
+      <c r="C956" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D956" s="6">
+        <v>1</v>
+      </c>
+      <c r="E956" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F956" s="6" t="s">
+        <v>1695</v>
+      </c>
+      <c r="G956" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J956" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L956" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N956" s="1">
+        <v>2</v>
+      </c>
+      <c r="O956" s="1">
+        <v>3</v>
+      </c>
+      <c r="P956" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="957" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A957" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B957" s="2">
+        <v>45183</v>
+      </c>
+      <c r="C957" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D957" s="6">
+        <v>1</v>
+      </c>
+      <c r="E957" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F957" s="6" t="s">
+        <v>1690</v>
+      </c>
+      <c r="G957" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H957" s="6" t="s">
+        <v>1557</v>
+      </c>
+      <c r="J957" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K957" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="N957" s="1">
+        <v>1</v>
+      </c>
+      <c r="O957" s="1">
+        <v>2</v>
+      </c>
+      <c r="P957" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="958" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A958" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B958" s="2">
+        <v>45184</v>
+      </c>
+      <c r="C958" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D958" s="6">
+        <v>1</v>
+      </c>
+      <c r="E958" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F958" s="6" t="s">
+        <v>1695</v>
+      </c>
+      <c r="G958" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J958" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L958" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N958" s="1">
+        <v>2</v>
+      </c>
+      <c r="O958" s="1">
+        <v>2</v>
+      </c>
+      <c r="P958" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="959" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A959" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B959" s="2">
+        <v>45185</v>
+      </c>
+      <c r="C959" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D959" s="6">
+        <v>1</v>
+      </c>
+      <c r="E959" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F959" s="6" t="s">
+        <v>1773</v>
+      </c>
+      <c r="G959" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J959" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L959" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N959" s="1">
+        <v>3</v>
+      </c>
+      <c r="O959" s="1">
+        <v>6</v>
+      </c>
+      <c r="P959" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="960" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A960" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B960" s="2">
+        <v>45185</v>
+      </c>
+      <c r="C960" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D960" s="6">
+        <v>1</v>
+      </c>
+      <c r="E960" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F960" s="6" t="s">
+        <v>1774</v>
+      </c>
+      <c r="G960" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K960" t="s">
+        <v>1775</v>
+      </c>
+      <c r="L960" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N960" s="1">
+        <v>2</v>
+      </c>
+      <c r="O960" s="1">
+        <v>3</v>
+      </c>
+      <c r="P960" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="961" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A961" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B961" s="2">
+        <v>45185</v>
+      </c>
+      <c r="C961" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D961" s="6">
+        <v>1</v>
+      </c>
+      <c r="E961" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F961" s="6" t="s">
+        <v>1776</v>
+      </c>
+      <c r="G961" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K961" t="s">
+        <v>1775</v>
+      </c>
+      <c r="L961" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N961" s="1">
+        <v>2</v>
+      </c>
+      <c r="O961" s="1">
+        <v>2</v>
+      </c>
+      <c r="P961" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="962" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A962" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B962" s="2">
+        <v>45187</v>
+      </c>
+      <c r="C962" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D962" s="6">
+        <v>1</v>
+      </c>
+      <c r="E962" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F962" s="6" t="s">
+        <v>1777</v>
+      </c>
+      <c r="G962" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J962" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="N962" s="1">
+        <v>3</v>
+      </c>
+      <c r="O962" s="1">
+        <v>7</v>
+      </c>
+      <c r="P962" t="s">
+        <v>35</v>
+      </c>
+      <c r="R962">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="963" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A963" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B963" s="2">
+        <v>45188</v>
+      </c>
+      <c r="C963" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D963" s="6">
+        <v>1</v>
+      </c>
+      <c r="E963" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F963" s="6" t="s">
+        <v>1774</v>
+      </c>
+      <c r="G963" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J963" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K963" s="6" t="s">
+        <v>1778</v>
+      </c>
+      <c r="L963" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N963" s="1">
+        <v>3</v>
+      </c>
+      <c r="O963" s="1">
+        <v>10</v>
+      </c>
+      <c r="P963" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="964" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A964" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B964" s="2">
+        <v>45191</v>
+      </c>
+      <c r="C964" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D964" s="6">
+        <v>1</v>
+      </c>
+      <c r="E964" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F964" s="6" t="s">
+        <v>1695</v>
+      </c>
+      <c r="G964" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J964" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L964" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N964" s="1">
+        <v>3</v>
+      </c>
+      <c r="O964" s="1">
+        <v>3</v>
+      </c>
+      <c r="P964" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="965" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A965" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B965" s="2">
+        <v>45195</v>
+      </c>
+      <c r="C965" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D965" s="6">
+        <v>1</v>
+      </c>
+      <c r="E965" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F965" s="6" t="s">
+        <v>1695</v>
+      </c>
+      <c r="G965" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J965" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K965" s="6" t="s">
+        <v>1779</v>
+      </c>
+      <c r="L965" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N965" s="1">
+        <v>3</v>
+      </c>
+      <c r="O965" s="1">
+        <v>4</v>
+      </c>
+      <c r="P965" t="s">
+        <v>35</v>
+      </c>
+      <c r="R965">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="966" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A966" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B966" s="2">
+        <v>45197</v>
+      </c>
+      <c r="C966" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D966" s="6">
+        <v>1</v>
+      </c>
+      <c r="E966" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F966" s="6" t="s">
+        <v>1688</v>
+      </c>
+      <c r="G966" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J966" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K966" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="L966" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N966" s="1">
+        <v>3</v>
+      </c>
+      <c r="O966" s="1">
+        <v>8</v>
+      </c>
+      <c r="P966" t="s">
+        <v>35</v>
+      </c>
+      <c r="R966">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="967" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A967" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B967" s="2">
+        <v>45197</v>
+      </c>
+      <c r="C967" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D967" s="6">
+        <v>1</v>
+      </c>
+      <c r="E967" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F967" s="6" t="s">
+        <v>1780</v>
+      </c>
+      <c r="G967" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J967" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L967" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N967" s="1">
+        <v>3</v>
+      </c>
+      <c r="O967" s="1">
+        <v>6</v>
+      </c>
+      <c r="P967" t="s">
+        <v>35</v>
+      </c>
+      <c r="R967">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="968" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A968" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B968" s="2">
+        <v>45199</v>
+      </c>
+      <c r="C968" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D968" s="6">
+        <v>1</v>
+      </c>
+      <c r="E968" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F968" s="6" t="s">
+        <v>1774</v>
+      </c>
+      <c r="G968" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J968" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L968" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N968" s="1">
+        <v>3</v>
+      </c>
+      <c r="O968" s="1">
+        <v>4</v>
+      </c>
+      <c r="P968" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="969" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A969" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B969" s="2">
+        <v>45199</v>
+      </c>
+      <c r="C969" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D969" s="6">
+        <v>1</v>
+      </c>
+      <c r="E969" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F969" s="6" t="s">
+        <v>1777</v>
+      </c>
+      <c r="G969" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J969" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L969" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N969" s="1">
+        <v>3</v>
+      </c>
+      <c r="O969" s="1">
+        <v>6</v>
+      </c>
+      <c r="P969" t="s">
+        <v>35</v>
+      </c>
+      <c r="R969">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="970" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A970" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B970" s="2">
+        <v>45200</v>
+      </c>
+      <c r="C970" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D970" s="6">
+        <v>1</v>
+      </c>
+      <c r="E970" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F970" s="6" t="s">
+        <v>1773</v>
+      </c>
+      <c r="G970" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J970" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K970" s="6" t="s">
+        <v>1779</v>
+      </c>
+      <c r="L970" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N970" s="1">
+        <v>3</v>
+      </c>
+      <c r="O970" s="1">
+        <v>4</v>
+      </c>
+      <c r="P970" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="971" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A971" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B971" s="2">
+        <v>45200</v>
+      </c>
+      <c r="C971" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D971" s="6">
+        <v>1</v>
+      </c>
+      <c r="E971" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F971" s="6" t="s">
+        <v>1690</v>
+      </c>
+      <c r="G971" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H971" s="6" t="s">
+        <v>1557</v>
+      </c>
+      <c r="J971" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L971" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N971" s="1">
+        <v>3</v>
+      </c>
+      <c r="O971" s="1">
+        <v>2</v>
+      </c>
+      <c r="P971" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="972" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A972" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B972" s="2">
+        <v>45202</v>
+      </c>
+      <c r="C972" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D972" s="6">
+        <v>1</v>
+      </c>
+      <c r="E972" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F972" s="6" t="s">
+        <v>1781</v>
+      </c>
+      <c r="G972" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J972" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L972" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N972" s="1">
+        <v>2</v>
+      </c>
+      <c r="O972" s="1">
+        <v>2</v>
+      </c>
+      <c r="P972" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="973" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A973" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B973" s="2">
+        <v>45203</v>
+      </c>
+      <c r="C973" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D973" s="6">
+        <v>1</v>
+      </c>
+      <c r="E973" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F973" s="6" t="s">
+        <v>1782</v>
+      </c>
+      <c r="G973" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K973" t="s">
+        <v>1775</v>
+      </c>
+      <c r="N973" s="1">
+        <v>3</v>
+      </c>
+      <c r="O973" s="1">
+        <v>6</v>
+      </c>
+      <c r="P973" t="s">
+        <v>35</v>
+      </c>
+      <c r="R973">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="974" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A974" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B974" s="2">
+        <v>45205</v>
+      </c>
+      <c r="C974" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D974" s="6">
+        <v>1</v>
+      </c>
+      <c r="E974" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F974" s="6" t="s">
+        <v>1772</v>
+      </c>
+      <c r="G974" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J974" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L974" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N974" s="1">
+        <v>3</v>
+      </c>
+      <c r="O974" s="1">
+        <v>7</v>
+      </c>
+      <c r="P974" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="975" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A975" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B975" s="2">
+        <v>45081</v>
+      </c>
+      <c r="C975" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D975" s="6">
+        <v>1</v>
+      </c>
+      <c r="E975" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F975" s="6" t="s">
+        <v>1783</v>
+      </c>
+      <c r="G975" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J975" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="L975" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N975" s="1">
+        <v>5</v>
+      </c>
+      <c r="O975" s="1">
+        <v>17</v>
+      </c>
+      <c r="P975" t="s">
+        <v>89</v>
+      </c>
+      <c r="R975">
+        <v>70</v>
+      </c>
+      <c r="S975" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="976" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A976" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B976" s="2">
+        <v>45087</v>
+      </c>
+      <c r="C976" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D976" s="6">
+        <v>1</v>
+      </c>
+      <c r="E976" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F976" s="6" t="s">
+        <v>1581</v>
+      </c>
+      <c r="G976" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J976" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="L976" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N976" s="1">
+        <v>6</v>
+      </c>
+      <c r="O976" s="1">
+        <v>20</v>
+      </c>
+      <c r="P976" t="s">
+        <v>89</v>
+      </c>
+      <c r="R976">
+        <v>70</v>
+      </c>
+      <c r="S976" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="977" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A977" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B977" s="2">
+        <v>45096</v>
+      </c>
+      <c r="C977" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D977" s="6">
+        <v>1</v>
+      </c>
+      <c r="E977" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F977" s="6" t="s">
+        <v>1585</v>
+      </c>
+      <c r="G977" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J977" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L977" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N977" s="1">
+        <v>4</v>
+      </c>
+      <c r="O977" s="1">
+        <v>8</v>
+      </c>
+      <c r="P977" t="s">
+        <v>35</v>
+      </c>
+      <c r="R977">
+        <v>100</v>
+      </c>
+      <c r="S977" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="978" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A978" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B978" s="2">
+        <v>45098</v>
+      </c>
+      <c r="C978" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D978" s="6">
+        <v>1</v>
+      </c>
+      <c r="E978" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F978" s="6" t="s">
+        <v>1583</v>
+      </c>
+      <c r="G978" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J978" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L978" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N978" s="1">
+        <v>4</v>
+      </c>
+      <c r="O978" s="1">
+        <v>10</v>
+      </c>
+      <c r="P978" t="s">
+        <v>35</v>
+      </c>
+      <c r="R978">
+        <v>100</v>
+      </c>
+      <c r="S978" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="979" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A979" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B979" s="2">
+        <v>45105</v>
+      </c>
+      <c r="C979" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D979" s="6">
+        <v>1</v>
+      </c>
+      <c r="E979" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F979" s="6" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G979" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J979" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L979" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N979" s="1">
+        <v>4</v>
+      </c>
+      <c r="O979" s="1">
+        <v>7</v>
+      </c>
+      <c r="P979" t="s">
+        <v>35</v>
+      </c>
+      <c r="R979">
+        <v>100</v>
+      </c>
+      <c r="S979" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="980" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A980" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B980" s="2">
+        <v>45117</v>
+      </c>
+      <c r="C980" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D980" s="6">
+        <v>1</v>
+      </c>
+      <c r="E980" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F980" s="6" t="s">
+        <v>1785</v>
+      </c>
+      <c r="G980" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J980" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="L980" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N980" s="1">
+        <v>6</v>
+      </c>
+      <c r="O980" s="1">
+        <v>25</v>
+      </c>
+      <c r="P980" t="s">
+        <v>89</v>
+      </c>
+      <c r="R980">
+        <v>70</v>
+      </c>
+      <c r="S980" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="981" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A981" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B981" s="2">
+        <v>45120</v>
+      </c>
+      <c r="C981" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D981" s="6">
+        <v>1</v>
+      </c>
+      <c r="E981" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F981" s="6" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G981" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J981" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L981" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N981" s="1">
+        <v>5</v>
+      </c>
+      <c r="O981" s="1">
+        <v>11</v>
+      </c>
+      <c r="P981" t="s">
+        <v>89</v>
+      </c>
+      <c r="R981">
+        <v>70</v>
+      </c>
+      <c r="S981" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="982" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A982" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B982" s="2">
+        <v>45124</v>
+      </c>
+      <c r="C982" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D982" s="6">
+        <v>1</v>
+      </c>
+      <c r="E982" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F982" s="6" t="s">
+        <v>1786</v>
+      </c>
+      <c r="G982" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J982" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L982" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N982" s="1">
+        <v>4</v>
+      </c>
+      <c r="O982" s="1">
+        <v>9</v>
+      </c>
+      <c r="P982" t="s">
+        <v>35</v>
+      </c>
+      <c r="R982">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="983" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A983" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B983" s="2">
+        <v>45126</v>
+      </c>
+      <c r="C983" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D983" s="6">
+        <v>1</v>
+      </c>
+      <c r="E983" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F983" s="6" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G983" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J983" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L983" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N983" s="1">
+        <v>4</v>
+      </c>
+      <c r="O983" s="1">
+        <v>15</v>
+      </c>
+      <c r="P983" t="s">
+        <v>35</v>
+      </c>
+      <c r="R983">
+        <v>100</v>
+      </c>
+      <c r="S983" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="984" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A984" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B984" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C984" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D984" s="6">
+        <v>1</v>
+      </c>
+      <c r="E984" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F984" s="6" t="s">
+        <v>1788</v>
+      </c>
+      <c r="G984" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J984" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L984" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N984" s="1">
+        <v>4</v>
+      </c>
+      <c r="O984" s="1">
+        <v>4</v>
+      </c>
+      <c r="P984" t="s">
+        <v>35</v>
+      </c>
+      <c r="R984">
+        <v>100</v>
+      </c>
+      <c r="S984" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="985" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A985" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B985" s="2">
+        <v>45135</v>
+      </c>
+      <c r="C985" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D985" s="6">
+        <v>1</v>
+      </c>
+      <c r="E985" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F985" s="6" t="s">
+        <v>1789</v>
+      </c>
+      <c r="G985" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J985" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L985" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N985" s="1">
+        <v>4</v>
+      </c>
+      <c r="O985" s="1">
+        <v>17</v>
+      </c>
+      <c r="P985" t="s">
+        <v>89</v>
+      </c>
+      <c r="R985">
+        <v>70</v>
+      </c>
+      <c r="S985" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="986" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A986" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B986" s="2">
+        <v>45136</v>
+      </c>
+      <c r="C986" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D986" s="6">
+        <v>1</v>
+      </c>
+      <c r="E986" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F986" s="6" t="s">
+        <v>1790</v>
+      </c>
+      <c r="G986" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J986" s="6" t="s">
+        <v>1791</v>
+      </c>
+      <c r="L986" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N986" s="1">
+        <v>6</v>
+      </c>
+      <c r="O986" s="1">
+        <v>23</v>
+      </c>
+      <c r="P986" t="s">
+        <v>89</v>
+      </c>
+      <c r="R986">
+        <v>70</v>
+      </c>
+      <c r="S986" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="987" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A987" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B987" s="2">
+        <v>45142</v>
+      </c>
+      <c r="C987" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D987" s="6">
+        <v>1</v>
+      </c>
+      <c r="E987" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F987" s="6" t="s">
+        <v>1792</v>
+      </c>
+      <c r="G987" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K987" t="s">
+        <v>1793</v>
+      </c>
+      <c r="L987" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N987" s="1">
+        <v>6</v>
+      </c>
+      <c r="O987" s="1">
+        <v>4</v>
+      </c>
+      <c r="P987" t="s">
+        <v>89</v>
+      </c>
+      <c r="R987">
+        <v>80</v>
+      </c>
+      <c r="S987" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="988" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A988" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B988" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C988" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D988" s="6">
+        <v>1</v>
+      </c>
+      <c r="E988" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F988" s="6" t="s">
+        <v>1794</v>
+      </c>
+      <c r="G988" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K988" t="s">
+        <v>1795</v>
+      </c>
+      <c r="L988" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N988" s="1">
+        <v>6</v>
+      </c>
+      <c r="O988" s="1">
+        <v>5</v>
+      </c>
+      <c r="P988" t="s">
+        <v>89</v>
+      </c>
+      <c r="R988">
+        <v>80</v>
+      </c>
+      <c r="S988" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="989" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A989" t="s">
+        <v>1723</v>
+      </c>
+      <c r="B989" s="2">
+        <v>45149</v>
+      </c>
+      <c r="C989" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D989" s="6">
+        <v>1</v>
+      </c>
+      <c r="E989" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F989" s="6" t="s">
+        <v>1796</v>
+      </c>
+      <c r="G989" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K989" t="s">
+        <v>1802</v>
+      </c>
+      <c r="L989" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N989" s="1">
+        <v>5</v>
+      </c>
+      <c r="O989" s="1">
+        <v>4</v>
+      </c>
+      <c r="P989" t="s">
+        <v>89</v>
+      </c>
+      <c r="R989">
+        <v>80</v>
+      </c>
+      <c r="S989" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="990" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A990" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B990" s="2">
+        <v>45172</v>
+      </c>
+      <c r="C990" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D990" s="6">
+        <v>1</v>
+      </c>
+      <c r="E990" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F990" s="6" t="s">
+        <v>1797</v>
+      </c>
+      <c r="G990" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K990" t="s">
+        <v>1801</v>
+      </c>
+      <c r="L990" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N990" s="1">
+        <v>4</v>
+      </c>
+      <c r="O990" s="1">
+        <v>7</v>
+      </c>
+      <c r="P990" t="s">
+        <v>89</v>
+      </c>
+      <c r="R990">
+        <v>80</v>
+      </c>
+      <c r="S990" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="991" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A991" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B991" s="2">
+        <v>45175</v>
+      </c>
+      <c r="C991" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D991" s="6">
+        <v>1</v>
+      </c>
+      <c r="E991" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F991" s="6" t="s">
+        <v>1798</v>
+      </c>
+      <c r="G991" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K991" t="s">
+        <v>1799</v>
+      </c>
+      <c r="L991" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N991" s="1">
+        <v>6</v>
+      </c>
+      <c r="O991" s="1">
+        <v>25</v>
+      </c>
+      <c r="P991" t="s">
+        <v>89</v>
+      </c>
+      <c r="R991">
+        <v>70</v>
+      </c>
+      <c r="S991" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="992" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A992" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B992" s="2">
+        <v>45180</v>
+      </c>
+      <c r="C992" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D992" s="6">
+        <v>1</v>
+      </c>
+      <c r="E992" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F992" s="6" t="s">
+        <v>1800</v>
+      </c>
+      <c r="G992" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K992" t="s">
+        <v>1801</v>
+      </c>
+      <c r="L992" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N992" s="1">
+        <v>6</v>
+      </c>
+      <c r="O992" s="1">
+        <v>25</v>
+      </c>
+      <c r="P992" t="s">
+        <v>89</v>
+      </c>
+      <c r="R992">
+        <v>70</v>
+      </c>
+      <c r="S992" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="993" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A993" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B993" s="2">
+        <v>45212</v>
+      </c>
+      <c r="C993" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D993" s="6">
+        <v>1</v>
+      </c>
+      <c r="E993" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F993" s="6" t="s">
+        <v>1792</v>
+      </c>
+      <c r="G993" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K993" t="s">
+        <v>1801</v>
+      </c>
+      <c r="L993" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N993" s="1">
+        <v>4</v>
+      </c>
+      <c r="O993" s="1">
+        <v>4</v>
+      </c>
+      <c r="P993" t="s">
+        <v>89</v>
+      </c>
+      <c r="R993">
+        <v>100</v>
+      </c>
+      <c r="S993" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="994" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A994" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B994" s="2">
+        <v>45212</v>
+      </c>
+      <c r="C994" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D994" s="6">
+        <v>1</v>
+      </c>
+      <c r="E994" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F994" s="6" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G994" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K994" t="s">
+        <v>1802</v>
+      </c>
+      <c r="L994" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N994" s="1">
+        <v>4</v>
+      </c>
+      <c r="O994" s="1">
+        <v>4</v>
+      </c>
+      <c r="P994" t="s">
+        <v>89</v>
+      </c>
+      <c r="R994">
+        <v>100</v>
+      </c>
+      <c r="S994" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="995" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A995" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B995" s="2">
+        <v>45213</v>
+      </c>
+      <c r="C995" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D995" s="6">
+        <v>1</v>
+      </c>
+      <c r="E995" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F995" s="6" t="s">
+        <v>1803</v>
+      </c>
+      <c r="G995" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K995" t="s">
+        <v>1804</v>
+      </c>
+      <c r="L995" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N995" s="1">
+        <v>3</v>
+      </c>
+      <c r="O995" s="1">
+        <v>15</v>
+      </c>
+      <c r="P995" t="s">
+        <v>35</v>
+      </c>
+      <c r="R995">
+        <v>100</v>
+      </c>
+      <c r="S995" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="996" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A996" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B996" s="2">
+        <v>45213</v>
+      </c>
+      <c r="C996" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D996" s="6">
+        <v>1</v>
+      </c>
+      <c r="E996" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F996" s="6" t="s">
+        <v>1805</v>
+      </c>
+      <c r="G996" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K996" t="s">
+        <v>1804</v>
+      </c>
+      <c r="L996" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N996" s="1">
+        <v>3</v>
+      </c>
+      <c r="O996" s="1">
+        <v>11</v>
+      </c>
+      <c r="P996" t="s">
+        <v>35</v>
+      </c>
+      <c r="R996">
+        <v>100</v>
+      </c>
+      <c r="S996" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="997" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A997" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B997" s="2">
+        <v>45214</v>
+      </c>
+      <c r="C997" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D997" s="6">
+        <v>1</v>
+      </c>
+      <c r="E997" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F997" s="6" t="s">
+        <v>1806</v>
+      </c>
+      <c r="G997" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J997" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="L997" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N997" s="1">
+        <v>4</v>
+      </c>
+      <c r="O997" s="1">
+        <v>20</v>
+      </c>
+      <c r="P997" t="s">
+        <v>89</v>
+      </c>
+      <c r="R997">
+        <v>60</v>
+      </c>
+      <c r="S997" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="998" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A998" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B998" s="2">
+        <v>45214</v>
+      </c>
+      <c r="C998" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D998" s="6">
+        <v>1</v>
+      </c>
+      <c r="E998" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F998" s="6" t="s">
+        <v>1790</v>
+      </c>
+      <c r="G998" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J998" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="L998" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N998" s="1">
+        <v>4</v>
+      </c>
+      <c r="O998" s="1">
+        <v>10</v>
+      </c>
+      <c r="P998" t="s">
+        <v>89</v>
+      </c>
+      <c r="R998">
+        <v>60</v>
+      </c>
+      <c r="S998" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="999" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A999" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B999" s="2">
+        <v>45214</v>
+      </c>
+      <c r="C999" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D999" s="6">
+        <v>1</v>
+      </c>
+      <c r="E999" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F999" s="6" t="s">
+        <v>1587</v>
+      </c>
+      <c r="G999" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J999" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="L999" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N999" s="1">
+        <v>4</v>
+      </c>
+      <c r="O999" s="1">
+        <v>9</v>
+      </c>
+      <c r="P999" t="s">
+        <v>89</v>
+      </c>
+      <c r="R999">
+        <v>60</v>
+      </c>
+      <c r="S999" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1000" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1000" s="2">
+        <v>45214</v>
+      </c>
+      <c r="C1000" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1000" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1000" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1000" s="6" t="s">
+        <v>1796</v>
+      </c>
+      <c r="G1000" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1000" t="s">
+        <v>1802</v>
+      </c>
+      <c r="L1000" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N1000" s="1">
+        <v>4</v>
+      </c>
+      <c r="O1000" s="1">
+        <v>2</v>
+      </c>
+      <c r="P1000" t="s">
+        <v>89</v>
+      </c>
+      <c r="R1000">
+        <v>100</v>
+      </c>
+      <c r="S1000" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1001" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B1001" s="2">
+        <v>45214</v>
+      </c>
+      <c r="C1001" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1001" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1001" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1001" s="6" t="s">
+        <v>1807</v>
+      </c>
+      <c r="G1001" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1001" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L1001" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N1001" s="1">
+        <v>5</v>
+      </c>
+      <c r="O1001" s="1">
+        <v>25</v>
+      </c>
+      <c r="P1001" t="s">
+        <v>89</v>
+      </c>
+      <c r="R1001">
+        <v>60</v>
+      </c>
+      <c r="S1001" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1002" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1003" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1004" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1005" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1006" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1007" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1008" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1009" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1010" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1011" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1012" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1013" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1014" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1015" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1016" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1017" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1018" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1019" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1020" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1021" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1022" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1023" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1024" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1025" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1026" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1027" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1028" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1029" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1030" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1031" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1032" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1033" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1034" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1035" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1036" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1037" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1038" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1039" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1040" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1041" t="s">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1042" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1043" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1044" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1045" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1046" t="s">
+        <v>1816</v>
       </c>
     </row>
   </sheetData>
@@ -79684,16 +86697,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="34" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1201</v>
       </c>
-      <c r="B1" s="8"/>
+      <c r="B1" s="10"/>
     </row>
     <row r="3" spans="1:2" ht="21" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="11" t="s">
         <v>1202</v>
       </c>
-      <c r="B3" s="9"/>
+      <c r="B3" s="11"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
